--- a/ongoing_bm/schedule.xlsx
+++ b/ongoing_bm/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Birdman/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF1D048-2BB6-1140-BA14-8B66231C3446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B405C8-23F2-1748-98A9-C6C42DC2F9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34800" yWindow="3200" windowWidth="29400" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="11">
   <si>
     <t>date</t>
   </si>
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -123,6 +123,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1286,7 +1287,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E1349"/>
+  <dimension ref="A1:E1455"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="6" width="12.6640625" style="1" customWidth="1"/>
@@ -16908,1817 +16909,4719 @@
       <c r="E1090" s="3"/>
     </row>
     <row r="1091" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1091" s="4"/>
-      <c r="B1091" s="3"/>
-      <c r="C1091" s="3"/>
+      <c r="A1091" s="4">
+        <v>45658</v>
+      </c>
+      <c r="B1091" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1091" s="3">
+        <v>1</v>
+      </c>
       <c r="D1091" s="3"/>
       <c r="E1091" s="3"/>
     </row>
     <row r="1092" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1092" s="4"/>
-      <c r="B1092" s="3"/>
+      <c r="A1092" s="4">
+        <v>45659</v>
+      </c>
+      <c r="B1092" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1092" s="3"/>
       <c r="D1092" s="3"/>
       <c r="E1092" s="3"/>
     </row>
     <row r="1093" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1093" s="4"/>
-      <c r="B1093" s="3"/>
+      <c r="A1093" s="4">
+        <v>45660</v>
+      </c>
+      <c r="B1093" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1093" s="3"/>
       <c r="D1093" s="3"/>
       <c r="E1093" s="3"/>
     </row>
     <row r="1094" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1094" s="4"/>
-      <c r="B1094" s="3"/>
+      <c r="A1094" s="4">
+        <v>45661</v>
+      </c>
+      <c r="B1094" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1094" s="3"/>
       <c r="D1094" s="3"/>
       <c r="E1094" s="3"/>
     </row>
     <row r="1095" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1095" s="4"/>
-      <c r="B1095" s="3"/>
+      <c r="A1095" s="4">
+        <v>45662</v>
+      </c>
+      <c r="B1095" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1095" s="3"/>
       <c r="D1095" s="3"/>
       <c r="E1095" s="3"/>
     </row>
     <row r="1096" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1096" s="4"/>
-      <c r="B1096" s="3"/>
-      <c r="C1096" s="3"/>
+      <c r="A1096" s="4">
+        <v>45663</v>
+      </c>
+      <c r="B1096" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1096" s="3">
+        <v>1</v>
+      </c>
       <c r="D1096" s="3"/>
       <c r="E1096" s="3"/>
     </row>
     <row r="1097" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1097" s="4"/>
-      <c r="B1097" s="3"/>
-      <c r="C1097" s="3"/>
+      <c r="A1097" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B1097" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1097" s="3">
+        <v>1</v>
+      </c>
       <c r="D1097" s="3"/>
       <c r="E1097" s="3"/>
     </row>
     <row r="1098" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1098" s="4"/>
-      <c r="B1098" s="3"/>
+      <c r="A1098" s="4">
+        <v>45665</v>
+      </c>
+      <c r="B1098" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1098" s="3"/>
       <c r="D1098" s="3"/>
       <c r="E1098" s="3"/>
     </row>
     <row r="1099" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1099" s="4"/>
-      <c r="B1099" s="3"/>
-      <c r="C1099" s="3"/>
+      <c r="A1099" s="4">
+        <v>45666</v>
+      </c>
+      <c r="B1099" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1099" s="3">
+        <v>1</v>
+      </c>
       <c r="D1099" s="3"/>
       <c r="E1099" s="3"/>
     </row>
     <row r="1100" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1100" s="4"/>
-      <c r="B1100" s="3"/>
-      <c r="C1100" s="3"/>
+      <c r="A1100" s="4">
+        <v>45667</v>
+      </c>
+      <c r="B1100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1100" s="3">
+        <v>1</v>
+      </c>
       <c r="D1100" s="3"/>
       <c r="E1100" s="3"/>
     </row>
     <row r="1101" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1101" s="4"/>
-      <c r="B1101" s="3"/>
+      <c r="A1101" s="4">
+        <v>45668</v>
+      </c>
+      <c r="B1101" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1101" s="3"/>
       <c r="D1101" s="3"/>
       <c r="E1101" s="3"/>
     </row>
     <row r="1102" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1102" s="4"/>
-      <c r="B1102" s="3"/>
+      <c r="A1102" s="4">
+        <v>45669</v>
+      </c>
+      <c r="B1102" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1102" s="3"/>
       <c r="D1102" s="3"/>
       <c r="E1102" s="3"/>
     </row>
     <row r="1103" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1103" s="4"/>
-      <c r="B1103" s="3"/>
-      <c r="C1103" s="3"/>
+      <c r="A1103" s="4">
+        <v>45670</v>
+      </c>
+      <c r="B1103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1103" s="3">
+        <v>1</v>
+      </c>
       <c r="D1103" s="3"/>
       <c r="E1103" s="3"/>
     </row>
     <row r="1104" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1104" s="4"/>
-      <c r="B1104" s="3"/>
-      <c r="C1104" s="3"/>
+      <c r="A1104" s="4">
+        <v>45671</v>
+      </c>
+      <c r="B1104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1104" s="3">
+        <v>1</v>
+      </c>
       <c r="D1104" s="3"/>
       <c r="E1104" s="3"/>
     </row>
     <row r="1105" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1105" s="4"/>
-      <c r="B1105" s="3"/>
+      <c r="A1105" s="4">
+        <v>45672</v>
+      </c>
+      <c r="B1105" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1105" s="3"/>
       <c r="D1105" s="3"/>
       <c r="E1105" s="3"/>
     </row>
     <row r="1106" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1106" s="4"/>
-      <c r="B1106" s="3"/>
-      <c r="C1106" s="3"/>
+      <c r="A1106" s="4">
+        <v>45673</v>
+      </c>
+      <c r="B1106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1106" s="3">
+        <v>1</v>
+      </c>
       <c r="D1106" s="3"/>
       <c r="E1106" s="3"/>
     </row>
     <row r="1107" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1107" s="4"/>
-      <c r="B1107" s="3"/>
+      <c r="A1107" s="4">
+        <v>45674</v>
+      </c>
+      <c r="B1107" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1107" s="3"/>
       <c r="D1107" s="3"/>
       <c r="E1107" s="3"/>
     </row>
     <row r="1108" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1108" s="4"/>
-      <c r="B1108" s="3"/>
-      <c r="C1108" s="3"/>
+      <c r="A1108" s="4">
+        <v>45675</v>
+      </c>
+      <c r="B1108" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1108" s="3">
+        <v>1</v>
+      </c>
       <c r="D1108" s="3"/>
       <c r="E1108" s="3"/>
     </row>
     <row r="1109" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1109" s="4"/>
-      <c r="B1109" s="3"/>
+      <c r="A1109" s="4">
+        <v>45676</v>
+      </c>
+      <c r="B1109" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1109" s="3"/>
       <c r="D1109" s="3"/>
       <c r="E1109" s="3"/>
     </row>
     <row r="1110" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1110" s="4"/>
-      <c r="B1110" s="3"/>
-      <c r="C1110" s="3"/>
+      <c r="A1110" s="4">
+        <v>45677</v>
+      </c>
+      <c r="B1110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1110" s="3">
+        <v>1</v>
+      </c>
       <c r="D1110" s="3"/>
       <c r="E1110" s="3"/>
     </row>
     <row r="1111" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1111" s="4"/>
-      <c r="B1111" s="3"/>
+      <c r="A1111" s="4">
+        <v>45678</v>
+      </c>
+      <c r="B1111" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1111" s="3"/>
       <c r="D1111" s="3"/>
       <c r="E1111" s="3"/>
     </row>
     <row r="1112" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1112" s="4"/>
-      <c r="B1112" s="3"/>
-      <c r="C1112" s="3"/>
+      <c r="A1112" s="4">
+        <v>45679</v>
+      </c>
+      <c r="B1112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1112" s="3">
+        <v>1</v>
+      </c>
       <c r="D1112" s="3"/>
       <c r="E1112" s="3"/>
     </row>
     <row r="1113" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1113" s="4"/>
-      <c r="B1113" s="3"/>
+      <c r="A1113" s="4">
+        <v>45680</v>
+      </c>
+      <c r="B1113" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1113" s="3"/>
       <c r="D1113" s="3"/>
       <c r="E1113" s="3"/>
     </row>
     <row r="1114" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1114" s="4"/>
-      <c r="B1114" s="3"/>
-      <c r="C1114" s="3"/>
+      <c r="A1114" s="4">
+        <v>45681</v>
+      </c>
+      <c r="B1114" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1114" s="3">
+        <v>1</v>
+      </c>
       <c r="D1114" s="3"/>
       <c r="E1114" s="3"/>
     </row>
     <row r="1115" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1115" s="4"/>
-      <c r="B1115" s="3"/>
+      <c r="A1115" s="4">
+        <v>45682</v>
+      </c>
+      <c r="B1115" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1115" s="3"/>
       <c r="D1115" s="3"/>
       <c r="E1115" s="3"/>
     </row>
     <row r="1116" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1116" s="4"/>
-      <c r="B1116" s="3"/>
-      <c r="C1116" s="3"/>
+      <c r="A1116" s="4">
+        <v>45683</v>
+      </c>
+      <c r="B1116" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1116" s="3">
+        <v>1</v>
+      </c>
       <c r="D1116" s="3"/>
       <c r="E1116" s="3"/>
     </row>
     <row r="1117" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1117" s="4"/>
-      <c r="B1117" s="3"/>
+      <c r="A1117" s="4">
+        <v>45684</v>
+      </c>
+      <c r="B1117" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1117" s="3"/>
       <c r="D1117" s="3"/>
       <c r="E1117" s="3"/>
     </row>
     <row r="1118" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1118" s="4"/>
-      <c r="B1118" s="3"/>
-      <c r="C1118" s="3"/>
+      <c r="A1118" s="4">
+        <v>45685</v>
+      </c>
+      <c r="B1118" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1118" s="3">
+        <v>1</v>
+      </c>
       <c r="D1118" s="3"/>
       <c r="E1118" s="3"/>
     </row>
     <row r="1119" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1119" s="4"/>
-      <c r="B1119" s="3"/>
-      <c r="C1119" s="3"/>
+      <c r="A1119" s="4">
+        <v>45686</v>
+      </c>
+      <c r="B1119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1119" s="3">
+        <v>1</v>
+      </c>
       <c r="D1119" s="3"/>
       <c r="E1119" s="3"/>
     </row>
     <row r="1120" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1120" s="4"/>
-      <c r="B1120" s="3"/>
+      <c r="A1120" s="4">
+        <v>45687</v>
+      </c>
+      <c r="B1120" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1120" s="3"/>
       <c r="D1120" s="3"/>
       <c r="E1120" s="3"/>
     </row>
     <row r="1121" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1121" s="4"/>
-      <c r="B1121" s="3"/>
-      <c r="C1121" s="3"/>
-      <c r="D1121" s="3"/>
+      <c r="A1121" s="4">
+        <v>45688</v>
+      </c>
+      <c r="B1121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1121" s="3">
+        <v>1</v>
+      </c>
       <c r="E1121" s="3"/>
     </row>
     <row r="1122" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1122" s="4"/>
-      <c r="B1122" s="3"/>
-      <c r="C1122" s="3"/>
+      <c r="A1122" s="4">
+        <v>45689</v>
+      </c>
+      <c r="B1122" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1122" s="3">
+        <v>1</v>
+      </c>
       <c r="D1122" s="3"/>
       <c r="E1122" s="3"/>
     </row>
     <row r="1123" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1123" s="4"/>
-      <c r="B1123" s="3"/>
-      <c r="C1123" s="3"/>
+      <c r="A1123" s="4">
+        <v>45690</v>
+      </c>
+      <c r="B1123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1123" s="3">
+        <v>1</v>
+      </c>
       <c r="D1123" s="3"/>
       <c r="E1123" s="3"/>
     </row>
     <row r="1124" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1124" s="4"/>
-      <c r="B1124" s="3"/>
+      <c r="A1124" s="4">
+        <v>45691</v>
+      </c>
+      <c r="B1124" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1124" s="3"/>
       <c r="D1124" s="3"/>
       <c r="E1124" s="3"/>
     </row>
     <row r="1125" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1125" s="4"/>
-      <c r="B1125" s="3"/>
+      <c r="A1125" s="4">
+        <v>45692</v>
+      </c>
+      <c r="B1125" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1125" s="3"/>
       <c r="D1125" s="3"/>
       <c r="E1125" s="3"/>
     </row>
     <row r="1126" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1126" s="4"/>
-      <c r="B1126" s="3"/>
+      <c r="A1126" s="4">
+        <v>45693</v>
+      </c>
+      <c r="B1126" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1126" s="3"/>
       <c r="D1126" s="3"/>
       <c r="E1126" s="3"/>
     </row>
     <row r="1127" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1127" s="4"/>
-      <c r="B1127" s="3"/>
+      <c r="A1127" s="4">
+        <v>45694</v>
+      </c>
+      <c r="B1127" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1127" s="3"/>
       <c r="D1127" s="3"/>
       <c r="E1127" s="3"/>
     </row>
     <row r="1128" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1128" s="4"/>
-      <c r="B1128" s="3"/>
+      <c r="A1128" s="4">
+        <v>45695</v>
+      </c>
+      <c r="B1128" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1128" s="3"/>
-      <c r="D1128" s="3"/>
+      <c r="D1128" s="3">
+        <v>1</v>
+      </c>
       <c r="E1128" s="3"/>
     </row>
     <row r="1129" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1129" s="4"/>
-      <c r="B1129" s="3"/>
-      <c r="C1129" s="3"/>
-      <c r="D1129" s="3"/>
+      <c r="A1129" s="4">
+        <v>45696</v>
+      </c>
+      <c r="B1129" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1129" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1129" s="3">
+        <v>1</v>
+      </c>
       <c r="E1129" s="3"/>
     </row>
     <row r="1130" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1130" s="4"/>
-      <c r="B1130" s="3"/>
-      <c r="C1130" s="3"/>
-      <c r="D1130" s="3"/>
+      <c r="A1130" s="4">
+        <v>45697</v>
+      </c>
+      <c r="B1130" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1130" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1130" s="3">
+        <v>1</v>
+      </c>
       <c r="E1130" s="3"/>
     </row>
     <row r="1131" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1131" s="4"/>
-      <c r="B1131" s="3"/>
+      <c r="A1131" s="4">
+        <v>45698</v>
+      </c>
+      <c r="B1131" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1131" s="3"/>
       <c r="D1131" s="3"/>
       <c r="E1131" s="3"/>
     </row>
     <row r="1132" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1132" s="4"/>
-      <c r="B1132" s="3"/>
-      <c r="C1132" s="3"/>
+      <c r="A1132" s="4">
+        <v>45699</v>
+      </c>
+      <c r="B1132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1132" s="3">
+        <v>1</v>
+      </c>
       <c r="D1132" s="3"/>
       <c r="E1132" s="3"/>
     </row>
     <row r="1133" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1133" s="4"/>
-      <c r="B1133" s="3"/>
+      <c r="A1133" s="4">
+        <v>45700</v>
+      </c>
+      <c r="B1133" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1133" s="3"/>
       <c r="D1133" s="3"/>
       <c r="E1133" s="3"/>
     </row>
     <row r="1134" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1134" s="4"/>
-      <c r="B1134" s="3"/>
+      <c r="A1134" s="4">
+        <v>45701</v>
+      </c>
+      <c r="B1134" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1134" s="3"/>
       <c r="D1134" s="3"/>
       <c r="E1134" s="3"/>
     </row>
     <row r="1135" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1135" s="4"/>
-      <c r="B1135" s="3"/>
+      <c r="A1135" s="4">
+        <v>45702</v>
+      </c>
+      <c r="B1135" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1135" s="3"/>
-      <c r="D1135" s="3"/>
+      <c r="D1135" s="3">
+        <v>1</v>
+      </c>
       <c r="E1135" s="3"/>
     </row>
     <row r="1136" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1136" s="4"/>
-      <c r="B1136" s="3"/>
-      <c r="C1136" s="3"/>
-      <c r="D1136" s="3"/>
+      <c r="A1136" s="4">
+        <v>45703</v>
+      </c>
+      <c r="B1136" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1136" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1136" s="3">
+        <v>1</v>
+      </c>
       <c r="E1136" s="3"/>
     </row>
     <row r="1137" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1137" s="4"/>
-      <c r="B1137" s="3"/>
-      <c r="C1137" s="3"/>
+      <c r="A1137" s="4">
+        <v>45704</v>
+      </c>
+      <c r="B1137" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1137" s="3">
+        <v>1</v>
+      </c>
       <c r="D1137" s="3"/>
       <c r="E1137" s="3"/>
     </row>
     <row r="1138" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1138" s="4"/>
-      <c r="B1138" s="3"/>
+      <c r="A1138" s="4">
+        <v>45705</v>
+      </c>
+      <c r="B1138" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1138" s="3"/>
       <c r="D1138" s="3"/>
       <c r="E1138" s="3"/>
     </row>
     <row r="1139" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1139" s="4"/>
-      <c r="B1139" s="3"/>
+      <c r="A1139" s="4">
+        <v>45706</v>
+      </c>
+      <c r="B1139" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1139" s="3"/>
       <c r="D1139" s="3"/>
       <c r="E1139" s="3"/>
     </row>
     <row r="1140" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1140" s="4"/>
-      <c r="B1140" s="3"/>
+      <c r="A1140" s="4">
+        <v>45707</v>
+      </c>
+      <c r="B1140" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1140" s="3"/>
       <c r="D1140" s="3"/>
       <c r="E1140" s="3"/>
     </row>
     <row r="1141" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1141" s="4"/>
-      <c r="B1141" s="3"/>
-      <c r="C1141" s="3"/>
+      <c r="A1141" s="4">
+        <v>45708</v>
+      </c>
+      <c r="B1141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1141" s="3">
+        <v>1</v>
+      </c>
       <c r="D1141" s="3"/>
       <c r="E1141" s="3"/>
     </row>
     <row r="1142" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1142" s="4"/>
-      <c r="B1142" s="3"/>
-      <c r="C1142" s="3"/>
-      <c r="D1142" s="3"/>
+      <c r="A1142" s="4">
+        <v>45709</v>
+      </c>
+      <c r="B1142" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1142" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1142" s="3">
+        <v>1</v>
+      </c>
       <c r="E1142" s="3"/>
     </row>
     <row r="1143" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1143" s="4"/>
-      <c r="B1143" s="3"/>
-      <c r="C1143" s="3"/>
-      <c r="D1143" s="3"/>
+      <c r="A1143" s="4">
+        <v>45710</v>
+      </c>
+      <c r="B1143" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1143" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1143" s="3">
+        <v>1</v>
+      </c>
       <c r="E1143" s="3"/>
     </row>
     <row r="1144" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1144" s="4"/>
-      <c r="B1144" s="3"/>
+      <c r="A1144" s="4">
+        <v>45711</v>
+      </c>
+      <c r="B1144" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1144" s="3"/>
       <c r="D1144" s="3"/>
       <c r="E1144" s="3"/>
     </row>
     <row r="1145" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1145" s="4"/>
-      <c r="B1145" s="3"/>
-      <c r="C1145" s="3"/>
+      <c r="A1145" s="4">
+        <v>45712</v>
+      </c>
+      <c r="B1145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1145" s="3">
+        <v>1</v>
+      </c>
       <c r="D1145" s="3"/>
       <c r="E1145" s="3"/>
     </row>
     <row r="1146" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1146" s="4"/>
-      <c r="B1146" s="3"/>
+      <c r="A1146" s="4">
+        <v>45713</v>
+      </c>
+      <c r="B1146" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1146" s="3"/>
       <c r="D1146" s="3"/>
       <c r="E1146" s="3"/>
     </row>
     <row r="1147" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1147" s="4"/>
-      <c r="B1147" s="3"/>
+      <c r="A1147" s="4">
+        <v>45714</v>
+      </c>
+      <c r="B1147" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1147" s="3"/>
       <c r="D1147" s="3"/>
       <c r="E1147" s="3"/>
     </row>
     <row r="1148" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1148" s="4"/>
-      <c r="B1148" s="3"/>
+      <c r="A1148" s="4">
+        <v>45715</v>
+      </c>
+      <c r="B1148" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1148" s="3"/>
       <c r="D1148" s="3"/>
       <c r="E1148" s="3"/>
     </row>
     <row r="1149" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1149" s="4"/>
-      <c r="B1149" s="3"/>
+      <c r="A1149" s="4">
+        <v>45716</v>
+      </c>
+      <c r="B1149" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1149" s="3"/>
-      <c r="D1149" s="3"/>
+      <c r="D1149" s="3">
+        <v>1</v>
+      </c>
       <c r="E1149" s="3"/>
     </row>
     <row r="1150" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1150" s="4"/>
-      <c r="B1150" s="3"/>
-      <c r="C1150" s="3"/>
-      <c r="D1150" s="3"/>
+      <c r="A1150" s="4">
+        <v>45717</v>
+      </c>
+      <c r="B1150" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1150" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1150" s="3">
+        <v>1</v>
+      </c>
       <c r="E1150" s="3"/>
     </row>
     <row r="1151" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1151" s="4"/>
-      <c r="B1151" s="3"/>
-      <c r="C1151" s="3"/>
+      <c r="A1151" s="4">
+        <v>45718</v>
+      </c>
+      <c r="B1151" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1151" s="3">
+        <v>1</v>
+      </c>
       <c r="D1151" s="3"/>
       <c r="E1151" s="3"/>
     </row>
     <row r="1152" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1152" s="4"/>
-      <c r="B1152" s="3"/>
+      <c r="A1152" s="4">
+        <v>45719</v>
+      </c>
+      <c r="B1152" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1152" s="3"/>
       <c r="D1152" s="3"/>
       <c r="E1152" s="3"/>
     </row>
     <row r="1153" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1153" s="4"/>
-      <c r="B1153" s="3"/>
+      <c r="A1153" s="4">
+        <v>45720</v>
+      </c>
+      <c r="B1153" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1153" s="3"/>
       <c r="D1153" s="3"/>
       <c r="E1153" s="3"/>
     </row>
     <row r="1154" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1154" s="4"/>
-      <c r="B1154" s="3"/>
+      <c r="A1154" s="4">
+        <v>45721</v>
+      </c>
+      <c r="B1154" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1154" s="3"/>
       <c r="D1154" s="3"/>
       <c r="E1154" s="3"/>
     </row>
     <row r="1155" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1155" s="4"/>
-      <c r="B1155" s="3"/>
-      <c r="C1155" s="3"/>
+      <c r="A1155" s="4">
+        <v>45722</v>
+      </c>
+      <c r="B1155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1155" s="3">
+        <v>1</v>
+      </c>
       <c r="D1155" s="3"/>
       <c r="E1155" s="3"/>
     </row>
     <row r="1156" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1156" s="4"/>
-      <c r="B1156" s="3"/>
-      <c r="C1156" s="3"/>
-      <c r="D1156" s="3"/>
+      <c r="A1156" s="4">
+        <v>45723</v>
+      </c>
+      <c r="B1156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1156" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1156" s="3">
+        <v>1</v>
+      </c>
       <c r="E1156" s="3"/>
     </row>
     <row r="1157" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1157" s="4"/>
-      <c r="B1157" s="3"/>
-      <c r="C1157" s="3"/>
-      <c r="D1157" s="3"/>
+      <c r="A1157" s="4">
+        <v>45724</v>
+      </c>
+      <c r="B1157" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1157" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1157" s="3">
+        <v>1</v>
+      </c>
       <c r="E1157" s="3"/>
     </row>
     <row r="1158" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1158" s="4"/>
-      <c r="B1158" s="3"/>
+      <c r="A1158" s="4">
+        <v>45725</v>
+      </c>
+      <c r="B1158" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1158" s="3"/>
       <c r="D1158" s="3"/>
       <c r="E1158" s="3"/>
     </row>
     <row r="1159" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1159" s="4"/>
-      <c r="B1159" s="3"/>
+      <c r="A1159" s="4">
+        <v>45726</v>
+      </c>
+      <c r="B1159" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1159" s="3"/>
       <c r="D1159" s="3"/>
       <c r="E1159" s="3"/>
     </row>
     <row r="1160" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1160" s="4"/>
-      <c r="B1160" s="3"/>
-      <c r="C1160" s="3"/>
+      <c r="A1160" s="4">
+        <v>45727</v>
+      </c>
+      <c r="B1160" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1160" s="3">
+        <v>1</v>
+      </c>
       <c r="D1160" s="3"/>
       <c r="E1160" s="3"/>
     </row>
     <row r="1161" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1161" s="4"/>
-      <c r="B1161" s="3"/>
-      <c r="C1161" s="3"/>
+      <c r="A1161" s="4">
+        <v>45728</v>
+      </c>
+      <c r="B1161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1161" s="3">
+        <v>1</v>
+      </c>
       <c r="D1161" s="3"/>
       <c r="E1161" s="3"/>
     </row>
     <row r="1162" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1162" s="4"/>
-      <c r="B1162" s="3"/>
+      <c r="A1162" s="4">
+        <v>45729</v>
+      </c>
+      <c r="B1162" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1162" s="3"/>
       <c r="D1162" s="3"/>
       <c r="E1162" s="3"/>
     </row>
     <row r="1163" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1163" s="4"/>
-      <c r="B1163" s="3"/>
-      <c r="C1163" s="3"/>
-      <c r="D1163" s="3"/>
+      <c r="A1163" s="4">
+        <v>45730</v>
+      </c>
+      <c r="B1163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1163" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1163" s="3">
+        <v>1</v>
+      </c>
       <c r="E1163" s="3"/>
     </row>
     <row r="1164" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1164" s="4"/>
-      <c r="B1164" s="3"/>
-      <c r="C1164" s="3"/>
-      <c r="D1164" s="3"/>
+      <c r="A1164" s="4">
+        <v>45731</v>
+      </c>
+      <c r="B1164" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1164" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1164" s="3">
+        <v>1</v>
+      </c>
       <c r="E1164" s="3"/>
     </row>
     <row r="1165" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1165" s="4"/>
-      <c r="B1165" s="3"/>
+      <c r="A1165" s="4">
+        <v>45732</v>
+      </c>
+      <c r="B1165" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1165" s="3"/>
       <c r="D1165" s="3"/>
       <c r="E1165" s="3"/>
     </row>
     <row r="1166" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1166" s="4"/>
-      <c r="B1166" s="3"/>
-      <c r="C1166" s="3"/>
+      <c r="A1166" s="4">
+        <v>45733</v>
+      </c>
+      <c r="B1166" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1166" s="3">
+        <v>1</v>
+      </c>
       <c r="D1166" s="3"/>
       <c r="E1166" s="3"/>
     </row>
     <row r="1167" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1167" s="4"/>
-      <c r="B1167" s="3"/>
+      <c r="A1167" s="4">
+        <v>45734</v>
+      </c>
+      <c r="B1167" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1167" s="3"/>
       <c r="D1167" s="3"/>
       <c r="E1167" s="3"/>
     </row>
     <row r="1168" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1168" s="4"/>
-      <c r="B1168" s="3"/>
-      <c r="C1168" s="3"/>
+      <c r="A1168" s="4">
+        <v>45735</v>
+      </c>
+      <c r="B1168" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1168" s="3">
+        <v>1</v>
+      </c>
       <c r="D1168" s="3"/>
       <c r="E1168" s="3"/>
     </row>
     <row r="1169" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1169" s="4"/>
-      <c r="B1169" s="3"/>
+      <c r="A1169" s="4">
+        <v>45736</v>
+      </c>
+      <c r="B1169" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1169" s="3"/>
       <c r="D1169" s="3"/>
       <c r="E1169" s="3"/>
     </row>
     <row r="1170" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1170" s="4"/>
-      <c r="B1170" s="3"/>
-      <c r="C1170" s="3"/>
-      <c r="D1170" s="3"/>
+      <c r="A1170" s="4">
+        <v>45737</v>
+      </c>
+      <c r="B1170" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1170" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1170" s="3">
+        <v>1</v>
+      </c>
       <c r="E1170" s="3"/>
     </row>
     <row r="1171" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1171" s="4"/>
-      <c r="B1171" s="3"/>
-      <c r="C1171" s="3"/>
-      <c r="D1171" s="3"/>
+      <c r="A1171" s="4">
+        <v>45738</v>
+      </c>
+      <c r="B1171" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1171" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1171" s="3">
+        <v>1</v>
+      </c>
       <c r="E1171" s="3"/>
     </row>
     <row r="1172" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1172" s="4"/>
-      <c r="B1172" s="3"/>
-      <c r="C1172" s="3"/>
+      <c r="A1172" s="4">
+        <v>45739</v>
+      </c>
+      <c r="B1172" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1172" s="3">
+        <v>1</v>
+      </c>
       <c r="D1172" s="3"/>
       <c r="E1172" s="3"/>
     </row>
     <row r="1173" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1173" s="4"/>
-      <c r="B1173" s="3"/>
+      <c r="A1173" s="4">
+        <v>45740</v>
+      </c>
+      <c r="B1173" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1173" s="3"/>
       <c r="D1173" s="3"/>
       <c r="E1173" s="3"/>
     </row>
     <row r="1174" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1174" s="4"/>
-      <c r="B1174" s="3"/>
+      <c r="A1174" s="4">
+        <v>45741</v>
+      </c>
+      <c r="B1174" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1174" s="3"/>
       <c r="D1174" s="3"/>
       <c r="E1174" s="3"/>
     </row>
     <row r="1175" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1175" s="4"/>
-      <c r="B1175" s="3"/>
+      <c r="A1175" s="4">
+        <v>45742</v>
+      </c>
+      <c r="B1175" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1175" s="3"/>
       <c r="D1175" s="3"/>
       <c r="E1175" s="3"/>
     </row>
     <row r="1176" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1176" s="4"/>
-      <c r="B1176" s="3"/>
+      <c r="A1176" s="4">
+        <v>45743</v>
+      </c>
+      <c r="B1176" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1176" s="3"/>
       <c r="D1176" s="3"/>
       <c r="E1176" s="3"/>
     </row>
     <row r="1177" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1177" s="4"/>
-      <c r="B1177" s="3"/>
-      <c r="C1177" s="3"/>
+      <c r="A1177" s="4">
+        <v>45744</v>
+      </c>
+      <c r="B1177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1177" s="3">
+        <v>1</v>
+      </c>
       <c r="D1177" s="3"/>
       <c r="E1177" s="3"/>
     </row>
     <row r="1178" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1178" s="4"/>
-      <c r="B1178" s="3"/>
-      <c r="C1178" s="3"/>
-      <c r="D1178" s="3"/>
+      <c r="A1178" s="4">
+        <v>45745</v>
+      </c>
+      <c r="B1178" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1178" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1178" s="3">
+        <v>1</v>
+      </c>
       <c r="E1178" s="3"/>
     </row>
     <row r="1179" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1179" s="4"/>
-      <c r="B1179" s="3"/>
-      <c r="C1179" s="3"/>
+      <c r="A1179" s="4">
+        <v>45746</v>
+      </c>
+      <c r="B1179" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1179" s="3">
+        <v>1</v>
+      </c>
       <c r="D1179" s="3"/>
       <c r="E1179" s="3"/>
     </row>
     <row r="1180" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1180" s="4"/>
-      <c r="B1180" s="3"/>
-      <c r="C1180" s="3"/>
+      <c r="A1180" s="4">
+        <v>45747</v>
+      </c>
+      <c r="B1180" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1180" s="3">
+        <v>1</v>
+      </c>
       <c r="D1180" s="3"/>
       <c r="E1180" s="3"/>
     </row>
     <row r="1181" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1181" s="4"/>
-      <c r="B1181" s="3"/>
+      <c r="A1181" s="4">
+        <v>45748</v>
+      </c>
+      <c r="B1181" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1181" s="3"/>
       <c r="D1181" s="3"/>
       <c r="E1181" s="3"/>
     </row>
     <row r="1182" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1182" s="4"/>
-      <c r="B1182" s="3"/>
+      <c r="A1182" s="4">
+        <v>45749</v>
+      </c>
+      <c r="B1182" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1182" s="3"/>
       <c r="D1182" s="3"/>
       <c r="E1182" s="3"/>
     </row>
     <row r="1183" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1183" s="4"/>
-      <c r="B1183" s="3"/>
+      <c r="A1183" s="4">
+        <v>45750</v>
+      </c>
+      <c r="B1183" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1183" s="3"/>
       <c r="D1183" s="3"/>
       <c r="E1183" s="3"/>
     </row>
     <row r="1184" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1184" s="4"/>
-      <c r="B1184" s="3"/>
-      <c r="C1184" s="3"/>
-      <c r="D1184" s="3"/>
+      <c r="A1184" s="4">
+        <v>45751</v>
+      </c>
+      <c r="B1184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1184" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1184" s="3">
+        <v>1</v>
+      </c>
       <c r="E1184" s="3"/>
     </row>
     <row r="1185" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1185" s="4"/>
-      <c r="B1185" s="3"/>
-      <c r="C1185" s="3"/>
-      <c r="D1185" s="3"/>
+      <c r="A1185" s="4">
+        <v>45752</v>
+      </c>
+      <c r="B1185" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1185" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1185" s="3">
+        <v>1</v>
+      </c>
       <c r="E1185" s="3"/>
     </row>
     <row r="1186" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1186" s="4"/>
-      <c r="B1186" s="3"/>
-      <c r="C1186" s="3"/>
+      <c r="A1186" s="4">
+        <v>45753</v>
+      </c>
+      <c r="B1186" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1186" s="3">
+        <v>1</v>
+      </c>
       <c r="D1186" s="3"/>
       <c r="E1186" s="3"/>
     </row>
     <row r="1187" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1187" s="4"/>
-      <c r="B1187" s="3"/>
+      <c r="A1187" s="4">
+        <v>45754</v>
+      </c>
+      <c r="B1187" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1187" s="3"/>
       <c r="D1187" s="3"/>
       <c r="E1187" s="3"/>
     </row>
     <row r="1188" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1188" s="4"/>
-      <c r="B1188" s="3"/>
+      <c r="A1188" s="4">
+        <v>45755</v>
+      </c>
+      <c r="B1188" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1188" s="3"/>
       <c r="D1188" s="3"/>
       <c r="E1188" s="3"/>
     </row>
     <row r="1189" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1189" s="4"/>
-      <c r="B1189" s="3"/>
+      <c r="A1189" s="4">
+        <v>45756</v>
+      </c>
+      <c r="B1189" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1189" s="3"/>
       <c r="D1189" s="3"/>
       <c r="E1189" s="3"/>
     </row>
     <row r="1190" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1190" s="4"/>
-      <c r="B1190" s="3"/>
-      <c r="C1190" s="3"/>
+      <c r="A1190" s="4">
+        <v>45757</v>
+      </c>
+      <c r="B1190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1190" s="3">
+        <v>1</v>
+      </c>
       <c r="D1190" s="3"/>
       <c r="E1190" s="3"/>
     </row>
     <row r="1191" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1191" s="4"/>
-      <c r="B1191" s="3"/>
-      <c r="C1191" s="3"/>
-      <c r="D1191" s="3"/>
+      <c r="A1191" s="4">
+        <v>45758</v>
+      </c>
+      <c r="B1191" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1191" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1191" s="3">
+        <v>1</v>
+      </c>
       <c r="E1191" s="3"/>
     </row>
     <row r="1192" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1192" s="4"/>
-      <c r="B1192" s="3"/>
-      <c r="C1192" s="3"/>
-      <c r="D1192" s="3"/>
+      <c r="A1192" s="4">
+        <v>45759</v>
+      </c>
+      <c r="B1192" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1192" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1192" s="3">
+        <v>1</v>
+      </c>
       <c r="E1192" s="3"/>
     </row>
     <row r="1193" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1193" s="4"/>
-      <c r="B1193" s="3"/>
-      <c r="C1193" s="3"/>
+      <c r="A1193" s="4">
+        <v>45760</v>
+      </c>
+      <c r="B1193" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1193" s="3">
+        <v>1</v>
+      </c>
       <c r="D1193" s="3"/>
       <c r="E1193" s="3"/>
     </row>
     <row r="1194" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1194" s="4"/>
-      <c r="B1194" s="3"/>
+      <c r="A1194" s="4">
+        <v>45761</v>
+      </c>
+      <c r="B1194" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1194" s="3"/>
       <c r="D1194" s="3"/>
       <c r="E1194" s="3"/>
     </row>
     <row r="1195" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1195" s="4"/>
-      <c r="B1195" s="3"/>
+      <c r="A1195" s="4">
+        <v>45762</v>
+      </c>
+      <c r="B1195" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1195" s="3"/>
       <c r="D1195" s="3"/>
       <c r="E1195" s="3"/>
     </row>
     <row r="1196" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1196" s="4"/>
-      <c r="B1196" s="3"/>
+      <c r="A1196" s="4">
+        <v>45763</v>
+      </c>
+      <c r="B1196" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1196" s="3"/>
       <c r="D1196" s="3"/>
       <c r="E1196" s="3"/>
     </row>
     <row r="1197" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1197" s="4"/>
-      <c r="B1197" s="3"/>
+      <c r="A1197" s="4">
+        <v>45764</v>
+      </c>
+      <c r="B1197" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1197" s="3"/>
-      <c r="D1197" s="3"/>
+      <c r="D1197" s="3">
+        <v>1</v>
+      </c>
       <c r="E1197" s="3"/>
     </row>
     <row r="1198" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1198" s="4"/>
-      <c r="B1198" s="3"/>
-      <c r="C1198" s="3"/>
+      <c r="A1198" s="4">
+        <v>45765</v>
+      </c>
+      <c r="B1198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1198" s="3">
+        <v>1</v>
+      </c>
       <c r="D1198" s="3"/>
       <c r="E1198" s="3"/>
     </row>
     <row r="1199" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1199" s="4"/>
-      <c r="B1199" s="3"/>
-      <c r="C1199" s="3"/>
-      <c r="D1199" s="3"/>
+      <c r="A1199" s="4">
+        <v>45766</v>
+      </c>
+      <c r="B1199" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1199" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1199" s="3">
+        <v>1</v>
+      </c>
       <c r="E1199" s="3"/>
     </row>
     <row r="1200" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1200" s="4"/>
-      <c r="B1200" s="3"/>
-      <c r="C1200" s="3"/>
+      <c r="A1200" s="4">
+        <v>45767</v>
+      </c>
+      <c r="B1200" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1200" s="3">
+        <v>1</v>
+      </c>
       <c r="D1200" s="3"/>
       <c r="E1200" s="3"/>
     </row>
     <row r="1201" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1201" s="4"/>
-      <c r="B1201" s="3"/>
-      <c r="C1201" s="3"/>
+      <c r="A1201" s="4">
+        <v>45768</v>
+      </c>
+      <c r="B1201" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1201" s="3">
+        <v>1</v>
+      </c>
       <c r="D1201" s="3"/>
       <c r="E1201" s="3"/>
     </row>
     <row r="1202" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1202" s="4"/>
-      <c r="B1202" s="3"/>
+      <c r="A1202" s="4">
+        <v>45769</v>
+      </c>
+      <c r="B1202" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1202" s="3"/>
       <c r="D1202" s="3"/>
       <c r="E1202" s="3"/>
     </row>
     <row r="1203" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1203" s="4"/>
-      <c r="B1203" s="3"/>
-      <c r="C1203" s="3"/>
+      <c r="A1203" s="4">
+        <v>45770</v>
+      </c>
+      <c r="B1203" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1203" s="3">
+        <v>1</v>
+      </c>
       <c r="D1203" s="3"/>
       <c r="E1203" s="3"/>
     </row>
     <row r="1204" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1204" s="4"/>
-      <c r="B1204" s="3"/>
+      <c r="A1204" s="4">
+        <v>45771</v>
+      </c>
+      <c r="B1204" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1204" s="3"/>
-      <c r="D1204" s="3"/>
+      <c r="D1204" s="3">
+        <v>1</v>
+      </c>
       <c r="E1204" s="3"/>
     </row>
     <row r="1205" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1205" s="4"/>
-      <c r="B1205" s="3"/>
-      <c r="C1205" s="3"/>
+      <c r="A1205" s="4">
+        <v>45772</v>
+      </c>
+      <c r="B1205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1205" s="3">
+        <v>1</v>
+      </c>
       <c r="D1205" s="3"/>
       <c r="E1205" s="3"/>
     </row>
     <row r="1206" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1206" s="4"/>
-      <c r="B1206" s="3"/>
+      <c r="A1206" s="4">
+        <v>45773</v>
+      </c>
+      <c r="B1206" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1206" s="3"/>
-      <c r="D1206" s="3"/>
+      <c r="D1206" s="3">
+        <v>1</v>
+      </c>
       <c r="E1206" s="3"/>
     </row>
     <row r="1207" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1207" s="4"/>
-      <c r="B1207" s="3"/>
-      <c r="C1207" s="3"/>
+      <c r="A1207" s="4">
+        <v>45774</v>
+      </c>
+      <c r="B1207" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1207" s="3">
+        <v>1</v>
+      </c>
       <c r="D1207" s="3"/>
       <c r="E1207" s="3"/>
     </row>
     <row r="1208" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1208" s="4"/>
-      <c r="B1208" s="3"/>
-      <c r="C1208" s="3"/>
+      <c r="A1208" s="4">
+        <v>45775</v>
+      </c>
+      <c r="B1208" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1208" s="3">
+        <v>1</v>
+      </c>
       <c r="D1208" s="3"/>
       <c r="E1208" s="3"/>
     </row>
     <row r="1209" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1209" s="4"/>
-      <c r="B1209" s="3"/>
+      <c r="A1209" s="4">
+        <v>45776</v>
+      </c>
+      <c r="B1209" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1209" s="3"/>
       <c r="D1209" s="3"/>
       <c r="E1209" s="3"/>
     </row>
     <row r="1210" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1210" s="4"/>
-      <c r="B1210" s="3"/>
+      <c r="A1210" s="4">
+        <v>45777</v>
+      </c>
+      <c r="B1210" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1210" s="3"/>
       <c r="D1210" s="3"/>
       <c r="E1210" s="3"/>
     </row>
     <row r="1211" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1211" s="4"/>
-      <c r="B1211" s="3"/>
+      <c r="A1211" s="4">
+        <v>45778</v>
+      </c>
+      <c r="B1211" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1211" s="3"/>
-      <c r="D1211" s="3"/>
+      <c r="D1211" s="3">
+        <v>1</v>
+      </c>
       <c r="E1211" s="3"/>
     </row>
     <row r="1212" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1212" s="4"/>
-      <c r="B1212" s="3"/>
-      <c r="C1212" s="3"/>
+      <c r="A1212" s="4">
+        <v>45779</v>
+      </c>
+      <c r="B1212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1212" s="3">
+        <v>1</v>
+      </c>
       <c r="D1212" s="3"/>
       <c r="E1212" s="3"/>
     </row>
     <row r="1213" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1213" s="4"/>
-      <c r="B1213" s="3"/>
-      <c r="C1213" s="3"/>
-      <c r="D1213" s="3"/>
+      <c r="A1213" s="4">
+        <v>45780</v>
+      </c>
+      <c r="B1213" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1213" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1213" s="3">
+        <v>1</v>
+      </c>
       <c r="E1213" s="3"/>
     </row>
     <row r="1214" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1214" s="4"/>
-      <c r="B1214" s="3"/>
-      <c r="C1214" s="3"/>
+      <c r="A1214" s="4">
+        <v>45781</v>
+      </c>
+      <c r="B1214" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1214" s="3">
+        <v>1</v>
+      </c>
       <c r="D1214" s="3"/>
       <c r="E1214" s="3"/>
     </row>
     <row r="1215" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1215" s="4"/>
-      <c r="B1215" s="3"/>
-      <c r="C1215" s="3"/>
-      <c r="D1215" s="3"/>
+      <c r="A1215" s="4">
+        <v>45782</v>
+      </c>
+      <c r="B1215" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1215" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1215" s="3">
+        <v>1</v>
+      </c>
       <c r="E1215" s="3"/>
     </row>
     <row r="1216" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1216" s="4"/>
-      <c r="B1216" s="3"/>
-      <c r="C1216" s="3"/>
-      <c r="D1216" s="3"/>
+      <c r="A1216" s="4">
+        <v>45783</v>
+      </c>
+      <c r="B1216" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1216" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1216" s="3">
+        <v>1</v>
+      </c>
       <c r="E1216" s="3"/>
     </row>
     <row r="1217" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1217" s="4"/>
-      <c r="B1217" s="3"/>
+      <c r="A1217" s="4">
+        <v>45784</v>
+      </c>
+      <c r="B1217" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1217" s="3"/>
-      <c r="D1217" s="3"/>
+      <c r="D1217" s="3">
+        <v>1</v>
+      </c>
       <c r="E1217" s="3"/>
     </row>
     <row r="1218" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1218" s="4"/>
-      <c r="B1218" s="3"/>
+      <c r="A1218" s="4">
+        <v>45785</v>
+      </c>
+      <c r="B1218" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1218" s="3"/>
-      <c r="D1218" s="3"/>
+      <c r="D1218" s="3">
+        <v>1</v>
+      </c>
       <c r="E1218" s="3"/>
     </row>
     <row r="1219" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1219" s="4"/>
-      <c r="B1219" s="3"/>
+      <c r="A1219" s="4">
+        <v>45786</v>
+      </c>
+      <c r="B1219" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1219" s="3"/>
       <c r="D1219" s="3"/>
       <c r="E1219" s="3"/>
     </row>
     <row r="1220" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1220" s="4"/>
-      <c r="B1220" s="3"/>
+      <c r="A1220" s="4">
+        <v>45787</v>
+      </c>
+      <c r="B1220" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1220" s="3"/>
-      <c r="D1220" s="3"/>
+      <c r="D1220" s="3">
+        <v>1</v>
+      </c>
       <c r="E1220" s="3"/>
     </row>
     <row r="1221" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1221" s="4"/>
-      <c r="B1221" s="3"/>
-      <c r="C1221" s="3"/>
+      <c r="A1221" s="4">
+        <v>45788</v>
+      </c>
+      <c r="B1221" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1221" s="3">
+        <v>1</v>
+      </c>
       <c r="D1221" s="3"/>
       <c r="E1221" s="3"/>
     </row>
     <row r="1222" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1222" s="4"/>
-      <c r="B1222" s="3"/>
+      <c r="A1222" s="4">
+        <v>45789</v>
+      </c>
+      <c r="B1222" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1222" s="3"/>
       <c r="D1222" s="3"/>
       <c r="E1222" s="3"/>
     </row>
     <row r="1223" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1223" s="4"/>
-      <c r="B1223" s="3"/>
-      <c r="C1223" s="3"/>
+      <c r="A1223" s="4">
+        <v>45790</v>
+      </c>
+      <c r="B1223" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1223" s="3">
+        <v>1</v>
+      </c>
       <c r="D1223" s="3"/>
       <c r="E1223" s="3"/>
     </row>
     <row r="1224" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1224" s="4"/>
-      <c r="B1224" s="3"/>
+      <c r="A1224" s="4">
+        <v>45791</v>
+      </c>
+      <c r="B1224" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1224" s="3"/>
       <c r="D1224" s="3"/>
       <c r="E1224" s="3"/>
     </row>
     <row r="1225" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1225" s="4"/>
-      <c r="B1225" s="3"/>
+      <c r="A1225" s="4">
+        <v>45792</v>
+      </c>
+      <c r="B1225" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1225" s="3"/>
       <c r="D1225" s="3"/>
       <c r="E1225" s="3"/>
     </row>
     <row r="1226" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1226" s="4"/>
-      <c r="B1226" s="3"/>
-      <c r="C1226" s="3"/>
-      <c r="D1226" s="3"/>
+      <c r="A1226" s="4">
+        <v>45793</v>
+      </c>
+      <c r="B1226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1226" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1226" s="3">
+        <v>1</v>
+      </c>
       <c r="E1226" s="3"/>
     </row>
     <row r="1227" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1227" s="4"/>
-      <c r="B1227" s="3"/>
-      <c r="C1227" s="3"/>
-      <c r="D1227" s="3"/>
+      <c r="A1227" s="4">
+        <v>45794</v>
+      </c>
+      <c r="B1227" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1227" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1227" s="3">
+        <v>1</v>
+      </c>
       <c r="E1227" s="3"/>
     </row>
     <row r="1228" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1228" s="4"/>
-      <c r="B1228" s="3"/>
-      <c r="C1228" s="3"/>
+      <c r="A1228" s="4">
+        <v>45795</v>
+      </c>
+      <c r="B1228" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1228" s="3">
+        <v>1</v>
+      </c>
       <c r="D1228" s="3"/>
       <c r="E1228" s="3"/>
     </row>
     <row r="1229" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1229" s="4"/>
-      <c r="B1229" s="3"/>
+      <c r="A1229" s="4">
+        <v>45796</v>
+      </c>
+      <c r="B1229" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1229" s="3"/>
       <c r="D1229" s="3"/>
       <c r="E1229" s="3"/>
     </row>
     <row r="1230" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1230" s="4"/>
-      <c r="B1230" s="3"/>
+      <c r="A1230" s="4">
+        <v>45797</v>
+      </c>
+      <c r="B1230" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1230" s="3"/>
       <c r="D1230" s="3"/>
       <c r="E1230" s="3"/>
     </row>
     <row r="1231" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1231" s="4"/>
-      <c r="B1231" s="3"/>
+      <c r="A1231" s="4">
+        <v>45798</v>
+      </c>
+      <c r="B1231" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1231" s="3"/>
       <c r="D1231" s="3"/>
       <c r="E1231" s="3"/>
     </row>
     <row r="1232" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1232" s="4"/>
-      <c r="B1232" s="3"/>
+      <c r="A1232" s="4">
+        <v>45799</v>
+      </c>
+      <c r="B1232" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1232" s="3"/>
-      <c r="D1232" s="3"/>
+      <c r="D1232" s="3">
+        <v>1</v>
+      </c>
       <c r="E1232" s="3"/>
     </row>
     <row r="1233" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1233" s="4"/>
-      <c r="B1233" s="3"/>
-      <c r="C1233" s="3"/>
-      <c r="D1233" s="3"/>
+      <c r="A1233" s="4">
+        <v>45800</v>
+      </c>
+      <c r="B1233" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1233" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1233" s="3">
+        <v>1</v>
+      </c>
       <c r="E1233" s="3"/>
     </row>
     <row r="1234" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1234" s="4"/>
-      <c r="B1234" s="3"/>
-      <c r="C1234" s="3"/>
-      <c r="D1234" s="3"/>
+      <c r="A1234" s="4">
+        <v>45801</v>
+      </c>
+      <c r="B1234" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1234" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1234" s="3">
+        <v>1</v>
+      </c>
       <c r="E1234" s="3"/>
     </row>
     <row r="1235" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1235" s="4"/>
-      <c r="B1235" s="3"/>
-      <c r="C1235" s="3"/>
+      <c r="A1235" s="4">
+        <v>45802</v>
+      </c>
+      <c r="B1235" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1235" s="3">
+        <v>1</v>
+      </c>
       <c r="D1235" s="3"/>
       <c r="E1235" s="3"/>
     </row>
     <row r="1236" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1236" s="4"/>
-      <c r="B1236" s="3"/>
+      <c r="A1236" s="4">
+        <v>45803</v>
+      </c>
+      <c r="B1236" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1236" s="3"/>
       <c r="D1236" s="3"/>
       <c r="E1236" s="3"/>
     </row>
     <row r="1237" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1237" s="4"/>
-      <c r="B1237" s="3"/>
+      <c r="A1237" s="4">
+        <v>45804</v>
+      </c>
+      <c r="B1237" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1237" s="3"/>
-      <c r="D1237" s="3"/>
+      <c r="D1237" s="3">
+        <v>1</v>
+      </c>
       <c r="E1237" s="3"/>
     </row>
     <row r="1238" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1238" s="4"/>
-      <c r="B1238" s="3"/>
-      <c r="C1238" s="3"/>
+      <c r="A1238" s="4">
+        <v>45805</v>
+      </c>
+      <c r="B1238" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1238" s="3">
+        <v>1</v>
+      </c>
       <c r="D1238" s="3"/>
       <c r="E1238" s="3"/>
     </row>
     <row r="1239" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1239" s="4"/>
-      <c r="B1239" s="3"/>
+      <c r="A1239" s="4">
+        <v>45806</v>
+      </c>
+      <c r="B1239" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1239" s="3"/>
       <c r="D1239" s="3"/>
       <c r="E1239" s="3"/>
     </row>
     <row r="1240" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1240" s="4"/>
-      <c r="B1240" s="3"/>
+      <c r="A1240" s="4">
+        <v>45807</v>
+      </c>
+      <c r="B1240" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1240" s="3"/>
-      <c r="D1240" s="3"/>
+      <c r="D1240" s="3">
+        <v>1</v>
+      </c>
       <c r="E1240" s="3"/>
     </row>
     <row r="1241" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1241" s="4"/>
-      <c r="B1241" s="3"/>
+      <c r="A1241" s="4">
+        <v>45808</v>
+      </c>
+      <c r="B1241" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1241" s="3"/>
-      <c r="D1241" s="3"/>
+      <c r="D1241" s="3">
+        <v>1</v>
+      </c>
       <c r="E1241" s="3"/>
     </row>
     <row r="1242" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1242" s="4"/>
-      <c r="B1242" s="3"/>
-      <c r="C1242" s="3"/>
+      <c r="A1242" s="4">
+        <v>45809</v>
+      </c>
+      <c r="B1242" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1242" s="3">
+        <v>1</v>
+      </c>
       <c r="D1242" s="3"/>
       <c r="E1242" s="3"/>
     </row>
     <row r="1243" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1243" s="4"/>
-      <c r="B1243" s="3"/>
-      <c r="C1243" s="3"/>
+      <c r="A1243" s="4">
+        <v>45810</v>
+      </c>
+      <c r="B1243" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1243" s="3">
+        <v>1</v>
+      </c>
       <c r="D1243" s="3"/>
       <c r="E1243" s="3"/>
     </row>
     <row r="1244" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1244" s="4"/>
-      <c r="B1244" s="3"/>
+      <c r="A1244" s="4">
+        <v>45811</v>
+      </c>
+      <c r="B1244" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1244" s="3"/>
       <c r="D1244" s="3"/>
       <c r="E1244" s="3"/>
     </row>
     <row r="1245" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1245" s="4"/>
-      <c r="B1245" s="3"/>
+      <c r="A1245" s="4">
+        <v>45812</v>
+      </c>
+      <c r="B1245" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1245" s="3"/>
       <c r="D1245" s="3"/>
       <c r="E1245" s="3"/>
     </row>
     <row r="1246" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1246" s="4"/>
-      <c r="B1246" s="3"/>
+      <c r="A1246" s="4">
+        <v>45813</v>
+      </c>
+      <c r="B1246" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1246" s="3"/>
       <c r="D1246" s="3"/>
       <c r="E1246" s="3"/>
     </row>
     <row r="1247" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1247" s="4"/>
-      <c r="B1247" s="3"/>
-      <c r="C1247" s="3"/>
-      <c r="D1247" s="3"/>
+      <c r="A1247" s="4">
+        <v>45814</v>
+      </c>
+      <c r="B1247" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1247" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1247" s="3">
+        <v>1</v>
+      </c>
       <c r="E1247" s="3"/>
     </row>
     <row r="1248" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1248" s="4"/>
-      <c r="B1248" s="3"/>
-      <c r="C1248" s="3"/>
-      <c r="D1248" s="3"/>
+      <c r="A1248" s="4">
+        <v>45815</v>
+      </c>
+      <c r="B1248" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1248" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1248" s="3">
+        <v>1</v>
+      </c>
       <c r="E1248" s="3"/>
     </row>
     <row r="1249" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1249" s="4"/>
-      <c r="B1249" s="3"/>
+      <c r="A1249" s="4">
+        <v>45816</v>
+      </c>
+      <c r="B1249" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1249" s="3"/>
       <c r="D1249" s="3"/>
       <c r="E1249" s="3"/>
     </row>
     <row r="1250" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1250" s="4"/>
-      <c r="B1250" s="3"/>
+      <c r="A1250" s="4">
+        <v>45817</v>
+      </c>
+      <c r="B1250" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1250" s="3"/>
       <c r="D1250" s="3"/>
       <c r="E1250" s="3"/>
     </row>
     <row r="1251" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1251" s="4"/>
-      <c r="B1251" s="3"/>
+      <c r="A1251" s="4">
+        <v>45818</v>
+      </c>
+      <c r="B1251" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1251" s="3"/>
       <c r="D1251" s="3"/>
       <c r="E1251" s="3"/>
     </row>
     <row r="1252" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1252" s="4"/>
-      <c r="B1252" s="3"/>
+      <c r="A1252" s="4">
+        <v>45819</v>
+      </c>
+      <c r="B1252" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1252" s="3"/>
       <c r="D1252" s="3"/>
       <c r="E1252" s="3"/>
     </row>
     <row r="1253" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1253" s="4"/>
-      <c r="B1253" s="3"/>
-      <c r="C1253" s="3"/>
+      <c r="A1253" s="4">
+        <v>45820</v>
+      </c>
+      <c r="B1253" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1253" s="3">
+        <v>1</v>
+      </c>
       <c r="D1253" s="3"/>
       <c r="E1253" s="3"/>
     </row>
     <row r="1254" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1254" s="4"/>
-      <c r="B1254" s="3"/>
-      <c r="C1254" s="3"/>
-      <c r="D1254" s="3"/>
+      <c r="A1254" s="4">
+        <v>45821</v>
+      </c>
+      <c r="B1254" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1254" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1254" s="3">
+        <v>1</v>
+      </c>
       <c r="E1254" s="3"/>
     </row>
     <row r="1255" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1255" s="4"/>
-      <c r="B1255" s="3"/>
-      <c r="C1255" s="3"/>
-      <c r="D1255" s="3"/>
+      <c r="A1255" s="4">
+        <v>45822</v>
+      </c>
+      <c r="B1255" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1255" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1255" s="3">
+        <v>1</v>
+      </c>
       <c r="E1255" s="3"/>
     </row>
     <row r="1256" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1256" s="4"/>
-      <c r="B1256" s="3"/>
-      <c r="C1256" s="3"/>
+      <c r="A1256" s="4">
+        <v>45823</v>
+      </c>
+      <c r="B1256" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1256" s="3">
+        <v>1</v>
+      </c>
       <c r="D1256" s="3"/>
       <c r="E1256" s="3"/>
     </row>
     <row r="1257" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1257" s="4"/>
-      <c r="B1257" s="3"/>
+      <c r="A1257" s="4">
+        <v>45824</v>
+      </c>
+      <c r="B1257" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1257" s="3"/>
       <c r="D1257" s="3"/>
       <c r="E1257" s="3"/>
     </row>
     <row r="1258" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1258" s="4"/>
-      <c r="B1258" s="3"/>
+      <c r="A1258" s="4">
+        <v>45825</v>
+      </c>
+      <c r="B1258" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1258" s="3"/>
       <c r="D1258" s="3"/>
       <c r="E1258" s="3"/>
     </row>
     <row r="1259" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1259" s="4"/>
-      <c r="B1259" s="3"/>
+      <c r="A1259" s="4">
+        <v>45826</v>
+      </c>
+      <c r="B1259" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1259" s="3"/>
       <c r="D1259" s="3"/>
       <c r="E1259" s="3"/>
     </row>
     <row r="1260" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1260" s="4"/>
-      <c r="B1260" s="3"/>
-      <c r="C1260" s="3"/>
+      <c r="A1260" s="4">
+        <v>45827</v>
+      </c>
+      <c r="B1260" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1260" s="3">
+        <v>1</v>
+      </c>
       <c r="D1260" s="3"/>
       <c r="E1260" s="3"/>
     </row>
     <row r="1261" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1261" s="4"/>
-      <c r="B1261" s="3"/>
+      <c r="A1261" s="4">
+        <v>45828</v>
+      </c>
+      <c r="B1261" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1261" s="3"/>
       <c r="D1261" s="3"/>
       <c r="E1261" s="3"/>
     </row>
     <row r="1262" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1262" s="4"/>
-      <c r="B1262" s="3"/>
-      <c r="C1262" s="3"/>
-      <c r="D1262" s="3"/>
+      <c r="A1262" s="4">
+        <v>45829</v>
+      </c>
+      <c r="B1262" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1262" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1262" s="3">
+        <v>1</v>
+      </c>
       <c r="E1262" s="3"/>
     </row>
     <row r="1263" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1263" s="4"/>
-      <c r="B1263" s="3"/>
-      <c r="C1263" s="3"/>
+      <c r="A1263" s="4">
+        <v>45830</v>
+      </c>
+      <c r="B1263" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1263" s="3">
+        <v>1</v>
+      </c>
       <c r="D1263" s="3"/>
       <c r="E1263" s="3"/>
     </row>
     <row r="1264" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1264" s="4"/>
-      <c r="B1264" s="3"/>
+      <c r="A1264" s="4">
+        <v>45831</v>
+      </c>
+      <c r="B1264" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1264" s="3"/>
       <c r="D1264" s="3"/>
       <c r="E1264" s="3"/>
     </row>
     <row r="1265" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1265" s="4"/>
-      <c r="B1265" s="3"/>
+      <c r="A1265" s="4">
+        <v>45832</v>
+      </c>
+      <c r="B1265" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1265" s="3"/>
       <c r="D1265" s="3"/>
       <c r="E1265" s="3"/>
     </row>
     <row r="1266" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1266" s="4"/>
-      <c r="B1266" s="3"/>
+      <c r="A1266" s="4">
+        <v>45833</v>
+      </c>
+      <c r="B1266" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1266" s="3"/>
       <c r="D1266" s="3"/>
       <c r="E1266" s="3"/>
     </row>
     <row r="1267" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1267" s="4"/>
-      <c r="B1267" s="3"/>
-      <c r="C1267" s="3"/>
+      <c r="A1267" s="4">
+        <v>45834</v>
+      </c>
+      <c r="B1267" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1267" s="3">
+        <v>1</v>
+      </c>
       <c r="D1267" s="3"/>
       <c r="E1267" s="3"/>
     </row>
     <row r="1268" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1268" s="4"/>
-      <c r="B1268" s="3"/>
+      <c r="A1268" s="4">
+        <v>45835</v>
+      </c>
+      <c r="B1268" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1268" s="3"/>
       <c r="D1268" s="3"/>
       <c r="E1268" s="3"/>
     </row>
     <row r="1269" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1269" s="4"/>
-      <c r="B1269" s="3"/>
-      <c r="C1269" s="3"/>
-      <c r="D1269" s="3"/>
+      <c r="A1269" s="4">
+        <v>45836</v>
+      </c>
+      <c r="B1269" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1269" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1269" s="3">
+        <v>1</v>
+      </c>
       <c r="E1269" s="3"/>
     </row>
     <row r="1270" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1270" s="4"/>
-      <c r="B1270" s="3"/>
-      <c r="C1270" s="3"/>
+      <c r="A1270" s="4">
+        <v>45837</v>
+      </c>
+      <c r="B1270" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1270" s="3">
+        <v>1</v>
+      </c>
       <c r="D1270" s="3"/>
       <c r="E1270" s="3"/>
     </row>
     <row r="1271" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1271" s="4"/>
-      <c r="B1271" s="3"/>
+      <c r="A1271" s="4">
+        <v>45838</v>
+      </c>
+      <c r="B1271" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1271" s="3"/>
       <c r="D1271" s="3"/>
       <c r="E1271" s="3"/>
     </row>
     <row r="1272" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1272" s="4"/>
-      <c r="B1272" s="3"/>
+      <c r="A1272" s="4">
+        <v>45839</v>
+      </c>
+      <c r="B1272" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1272" s="3"/>
-      <c r="D1272" s="3"/>
+      <c r="D1272" s="3">
+        <v>1</v>
+      </c>
       <c r="E1272" s="3"/>
     </row>
     <row r="1273" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1273" s="4"/>
-      <c r="B1273" s="3"/>
-      <c r="C1273" s="3"/>
-      <c r="D1273" s="3"/>
+      <c r="A1273" s="4">
+        <v>45840</v>
+      </c>
+      <c r="B1273" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1273" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1273" s="3">
+        <v>1</v>
+      </c>
       <c r="E1273" s="3"/>
     </row>
     <row r="1274" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1274" s="4"/>
-      <c r="B1274" s="3"/>
-      <c r="C1274" s="3"/>
+      <c r="A1274" s="4">
+        <v>45841</v>
+      </c>
+      <c r="B1274" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1274" s="3">
+        <v>1</v>
+      </c>
       <c r="D1274" s="3"/>
       <c r="E1274" s="3"/>
     </row>
     <row r="1275" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1275" s="4"/>
-      <c r="B1275" s="3"/>
-      <c r="C1275" s="3"/>
-      <c r="D1275" s="3"/>
+      <c r="A1275" s="4">
+        <v>45842</v>
+      </c>
+      <c r="B1275" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1275" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1275" s="3">
+        <v>1</v>
+      </c>
       <c r="E1275" s="3"/>
     </row>
     <row r="1276" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1276" s="4"/>
-      <c r="B1276" s="3"/>
-      <c r="C1276" s="3"/>
-      <c r="D1276" s="3"/>
+      <c r="A1276" s="4">
+        <v>45843</v>
+      </c>
+      <c r="B1276" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1276" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1276" s="3">
+        <v>1</v>
+      </c>
       <c r="E1276" s="3"/>
     </row>
     <row r="1277" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1277" s="4"/>
-      <c r="B1277" s="3"/>
-      <c r="C1277" s="3"/>
+      <c r="A1277" s="4">
+        <v>45844</v>
+      </c>
+      <c r="B1277" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1277" s="3">
+        <v>1</v>
+      </c>
       <c r="D1277" s="3"/>
       <c r="E1277" s="3"/>
     </row>
     <row r="1278" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1278" s="4"/>
-      <c r="B1278" s="3"/>
+      <c r="A1278" s="4">
+        <v>45845</v>
+      </c>
+      <c r="B1278" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1278" s="3"/>
       <c r="D1278" s="3"/>
       <c r="E1278" s="3"/>
     </row>
     <row r="1279" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1279" s="4"/>
-      <c r="B1279" s="3"/>
+      <c r="A1279" s="4">
+        <v>45846</v>
+      </c>
+      <c r="B1279" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1279" s="3"/>
       <c r="D1279" s="3"/>
       <c r="E1279" s="3"/>
     </row>
     <row r="1280" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1280" s="4"/>
-      <c r="B1280" s="3"/>
+      <c r="A1280" s="4">
+        <v>45847</v>
+      </c>
+      <c r="B1280" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1280" s="3"/>
       <c r="D1280" s="3"/>
       <c r="E1280" s="3"/>
     </row>
     <row r="1281" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1281" s="4"/>
-      <c r="B1281" s="3"/>
-      <c r="C1281" s="3"/>
+      <c r="A1281" s="4">
+        <v>45848</v>
+      </c>
+      <c r="B1281" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1281" s="3">
+        <v>1</v>
+      </c>
       <c r="D1281" s="3"/>
       <c r="E1281" s="3"/>
     </row>
     <row r="1282" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1282" s="4"/>
-      <c r="B1282" s="3"/>
+      <c r="A1282" s="4">
+        <v>45849</v>
+      </c>
+      <c r="B1282" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1282" s="3"/>
       <c r="D1282" s="3"/>
       <c r="E1282" s="3"/>
     </row>
     <row r="1283" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1283" s="4"/>
-      <c r="B1283" s="3"/>
-      <c r="C1283" s="3"/>
-      <c r="D1283" s="3"/>
+      <c r="A1283" s="4">
+        <v>45850</v>
+      </c>
+      <c r="B1283" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1283" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1283" s="3">
+        <v>1</v>
+      </c>
       <c r="E1283" s="3"/>
     </row>
     <row r="1284" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1284" s="4"/>
-      <c r="B1284" s="3"/>
-      <c r="C1284" s="3"/>
+      <c r="A1284" s="4">
+        <v>45851</v>
+      </c>
+      <c r="B1284" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1284" s="3">
+        <v>1</v>
+      </c>
       <c r="D1284" s="3"/>
       <c r="E1284" s="3"/>
     </row>
     <row r="1285" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1285" s="4"/>
-      <c r="B1285" s="3"/>
-      <c r="C1285" s="3"/>
+      <c r="A1285" s="4">
+        <v>45852</v>
+      </c>
+      <c r="B1285" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1285" s="3">
+        <v>1</v>
+      </c>
       <c r="D1285" s="3"/>
       <c r="E1285" s="3"/>
     </row>
     <row r="1286" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1286" s="4"/>
-      <c r="B1286" s="3"/>
+      <c r="A1286" s="4">
+        <v>45853</v>
+      </c>
+      <c r="B1286" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1286" s="3"/>
-      <c r="D1286" s="3"/>
+      <c r="D1286" s="3">
+        <v>1</v>
+      </c>
       <c r="E1286" s="3"/>
     </row>
     <row r="1287" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1287" s="4"/>
-      <c r="B1287" s="3"/>
-      <c r="C1287" s="3"/>
+      <c r="A1287" s="4">
+        <v>45854</v>
+      </c>
+      <c r="B1287" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1287" s="3">
+        <v>1</v>
+      </c>
       <c r="D1287" s="3"/>
       <c r="E1287" s="3"/>
     </row>
     <row r="1288" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1288" s="4"/>
-      <c r="B1288" s="3"/>
+      <c r="A1288" s="4">
+        <v>45855</v>
+      </c>
+      <c r="B1288" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1288" s="3"/>
       <c r="D1288" s="3"/>
       <c r="E1288" s="3"/>
     </row>
     <row r="1289" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1289" s="4"/>
-      <c r="B1289" s="3"/>
+      <c r="A1289" s="4">
+        <v>45856</v>
+      </c>
+      <c r="B1289" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1289" s="3"/>
-      <c r="D1289" s="3"/>
+      <c r="D1289" s="3">
+        <v>1</v>
+      </c>
       <c r="E1289" s="3"/>
     </row>
     <row r="1290" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1290" s="4"/>
-      <c r="B1290" s="3"/>
-      <c r="C1290" s="3"/>
-      <c r="D1290" s="3"/>
+      <c r="A1290" s="4">
+        <v>45857</v>
+      </c>
+      <c r="B1290" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1290" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1290" s="3">
+        <v>1</v>
+      </c>
       <c r="E1290" s="3"/>
     </row>
     <row r="1291" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1291" s="4"/>
-      <c r="B1291" s="3"/>
-      <c r="C1291" s="3"/>
+      <c r="A1291" s="4">
+        <v>45858</v>
+      </c>
+      <c r="B1291" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1291" s="3">
+        <v>1</v>
+      </c>
       <c r="D1291" s="3"/>
       <c r="E1291" s="3"/>
     </row>
     <row r="1292" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1292" s="4"/>
-      <c r="B1292" s="3"/>
+      <c r="A1292" s="4">
+        <v>45859</v>
+      </c>
+      <c r="B1292" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1292" s="3"/>
       <c r="D1292" s="3"/>
       <c r="E1292" s="3"/>
     </row>
     <row r="1293" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1293" s="4"/>
-      <c r="B1293" s="3"/>
-      <c r="C1293" s="3"/>
+      <c r="A1293" s="4">
+        <v>45860</v>
+      </c>
+      <c r="B1293" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1293" s="3">
+        <v>1</v>
+      </c>
       <c r="D1293" s="3"/>
       <c r="E1293" s="3"/>
     </row>
     <row r="1294" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1294" s="4"/>
-      <c r="B1294" s="3"/>
+      <c r="A1294" s="4">
+        <v>45861</v>
+      </c>
+      <c r="B1294" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1294" s="3"/>
       <c r="D1294" s="3"/>
       <c r="E1294" s="3"/>
     </row>
     <row r="1295" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1295" s="4"/>
-      <c r="B1295" s="3"/>
+      <c r="A1295" s="4">
+        <v>45862</v>
+      </c>
+      <c r="B1295" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1295" s="3"/>
       <c r="D1295" s="3"/>
       <c r="E1295" s="3"/>
     </row>
     <row r="1296" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1296" s="4"/>
-      <c r="B1296" s="3"/>
+      <c r="A1296" s="4">
+        <v>45863</v>
+      </c>
+      <c r="B1296" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1296" s="3"/>
-      <c r="D1296" s="3"/>
+      <c r="D1296" s="3">
+        <v>1</v>
+      </c>
       <c r="E1296" s="3"/>
     </row>
     <row r="1297" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1297" s="4"/>
-      <c r="B1297" s="3"/>
-      <c r="C1297" s="3"/>
+      <c r="A1297" s="4">
+        <v>45864</v>
+      </c>
+      <c r="B1297" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1297" s="3">
+        <v>1</v>
+      </c>
       <c r="D1297" s="3"/>
       <c r="E1297" s="3"/>
     </row>
     <row r="1298" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1298" s="4"/>
-      <c r="B1298" s="3"/>
+      <c r="A1298" s="4">
+        <v>45865</v>
+      </c>
+      <c r="B1298" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1298" s="3"/>
       <c r="D1298" s="3"/>
       <c r="E1298" s="3"/>
     </row>
     <row r="1299" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1299" s="4"/>
-      <c r="B1299" s="3"/>
-      <c r="C1299" s="3"/>
+      <c r="A1299" s="4">
+        <v>45866</v>
+      </c>
+      <c r="B1299" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1299" s="3">
+        <v>1</v>
+      </c>
       <c r="D1299" s="3"/>
       <c r="E1299" s="3"/>
     </row>
     <row r="1300" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1300" s="4"/>
-      <c r="B1300" s="3"/>
+      <c r="A1300" s="4">
+        <v>45867</v>
+      </c>
+      <c r="B1300" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1300" s="3"/>
       <c r="D1300" s="3"/>
       <c r="E1300" s="3"/>
     </row>
     <row r="1301" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1301" s="4"/>
-      <c r="B1301" s="3"/>
+      <c r="A1301" s="4">
+        <v>45868</v>
+      </c>
+      <c r="B1301" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1301" s="3"/>
       <c r="D1301" s="3"/>
       <c r="E1301" s="3"/>
     </row>
     <row r="1302" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1302" s="4"/>
-      <c r="B1302" s="3"/>
-      <c r="C1302" s="3"/>
+      <c r="A1302" s="4">
+        <v>45869</v>
+      </c>
+      <c r="B1302" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1302" s="3">
+        <v>1</v>
+      </c>
       <c r="D1302" s="3"/>
       <c r="E1302" s="3"/>
     </row>
     <row r="1303" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1303" s="4"/>
-      <c r="B1303" s="3"/>
-      <c r="C1303" s="3"/>
+      <c r="A1303" s="4">
+        <v>45870</v>
+      </c>
+      <c r="B1303" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1303" s="3">
+        <v>1</v>
+      </c>
       <c r="D1303" s="3"/>
       <c r="E1303" s="3"/>
     </row>
     <row r="1304" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1304" s="4"/>
-      <c r="B1304" s="3"/>
+      <c r="A1304" s="4">
+        <v>45871</v>
+      </c>
+      <c r="B1304" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1304" s="3"/>
-      <c r="D1304" s="3"/>
+      <c r="D1304" s="3">
+        <v>1</v>
+      </c>
       <c r="E1304" s="3"/>
     </row>
     <row r="1305" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1305" s="4"/>
-      <c r="B1305" s="3"/>
-      <c r="C1305" s="3"/>
-      <c r="D1305" s="3"/>
+      <c r="A1305" s="4">
+        <v>45872</v>
+      </c>
+      <c r="B1305" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1305" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1305" s="3">
+        <v>1</v>
+      </c>
       <c r="E1305" s="3"/>
     </row>
     <row r="1306" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1306" s="4"/>
-      <c r="B1306" s="3"/>
+      <c r="A1306" s="4">
+        <v>45873</v>
+      </c>
+      <c r="B1306" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1306" s="3"/>
       <c r="D1306" s="3"/>
       <c r="E1306" s="3"/>
     </row>
     <row r="1307" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1307" s="4"/>
-      <c r="B1307" s="3"/>
-      <c r="C1307" s="3"/>
+      <c r="A1307" s="4">
+        <v>45874</v>
+      </c>
+      <c r="B1307" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1307" s="3">
+        <v>1</v>
+      </c>
       <c r="D1307" s="3"/>
       <c r="E1307" s="3"/>
     </row>
     <row r="1308" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1308" s="4"/>
-      <c r="B1308" s="3"/>
+      <c r="A1308" s="4">
+        <v>45875</v>
+      </c>
+      <c r="B1308" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1308" s="3"/>
       <c r="D1308" s="3"/>
       <c r="E1308" s="3"/>
     </row>
     <row r="1309" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1309" s="4"/>
-      <c r="B1309" s="3"/>
-      <c r="C1309" s="3"/>
+      <c r="A1309" s="4">
+        <v>45876</v>
+      </c>
+      <c r="B1309" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1309" s="3">
+        <v>1</v>
+      </c>
       <c r="D1309" s="3"/>
       <c r="E1309" s="3"/>
     </row>
     <row r="1310" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1310" s="4"/>
-      <c r="B1310" s="3"/>
+      <c r="A1310" s="4">
+        <v>45877</v>
+      </c>
+      <c r="B1310" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1310" s="3"/>
-      <c r="D1310" s="3"/>
+      <c r="D1310" s="3">
+        <v>1</v>
+      </c>
       <c r="E1310" s="3"/>
     </row>
     <row r="1311" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1311" s="4"/>
-      <c r="B1311" s="3"/>
-      <c r="C1311" s="3"/>
-      <c r="D1311" s="3"/>
+      <c r="A1311" s="4">
+        <v>45878</v>
+      </c>
+      <c r="B1311" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1311" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1311" s="3">
+        <v>1</v>
+      </c>
       <c r="E1311" s="3"/>
     </row>
     <row r="1312" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1312" s="4"/>
-      <c r="B1312" s="3"/>
-      <c r="C1312" s="3"/>
+      <c r="A1312" s="4">
+        <v>45879</v>
+      </c>
+      <c r="B1312" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1312" s="3">
+        <v>1</v>
+      </c>
       <c r="D1312" s="3"/>
       <c r="E1312" s="3"/>
     </row>
     <row r="1313" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1313" s="4"/>
-      <c r="B1313" s="3"/>
+      <c r="A1313" s="4">
+        <v>45880</v>
+      </c>
+      <c r="B1313" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1313" s="3"/>
       <c r="D1313" s="3"/>
       <c r="E1313" s="3"/>
     </row>
     <row r="1314" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1314" s="4"/>
-      <c r="B1314" s="3"/>
+      <c r="A1314" s="4">
+        <v>45881</v>
+      </c>
+      <c r="B1314" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1314" s="3"/>
       <c r="D1314" s="3"/>
       <c r="E1314" s="3"/>
     </row>
     <row r="1315" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1315" s="4"/>
-      <c r="B1315" s="3"/>
+      <c r="A1315" s="4">
+        <v>45882</v>
+      </c>
+      <c r="B1315" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1315" s="3"/>
       <c r="D1315" s="3"/>
       <c r="E1315" s="3"/>
     </row>
     <row r="1316" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1316" s="4"/>
-      <c r="B1316" s="3"/>
-      <c r="C1316" s="3"/>
+      <c r="A1316" s="4">
+        <v>45883</v>
+      </c>
+      <c r="B1316" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1316" s="3">
+        <v>1</v>
+      </c>
       <c r="D1316" s="3"/>
       <c r="E1316" s="3"/>
     </row>
     <row r="1317" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1317" s="4"/>
-      <c r="B1317" s="3"/>
+      <c r="A1317" s="4">
+        <v>45884</v>
+      </c>
+      <c r="B1317" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1317" s="3"/>
-      <c r="D1317" s="3"/>
+      <c r="D1317" s="3">
+        <v>1</v>
+      </c>
       <c r="E1317" s="3"/>
     </row>
     <row r="1318" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1318" s="4"/>
-      <c r="B1318" s="3"/>
-      <c r="C1318" s="3"/>
-      <c r="D1318" s="3"/>
+      <c r="A1318" s="4">
+        <v>45885</v>
+      </c>
+      <c r="B1318" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1318" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1318" s="3">
+        <v>1</v>
+      </c>
       <c r="E1318" s="3"/>
     </row>
     <row r="1319" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1319" s="4"/>
-      <c r="B1319" s="3"/>
+      <c r="A1319" s="4">
+        <v>45886</v>
+      </c>
+      <c r="B1319" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1319" s="3"/>
       <c r="D1319" s="3"/>
       <c r="E1319" s="3"/>
     </row>
     <row r="1320" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1320" s="4"/>
-      <c r="B1320" s="3"/>
-      <c r="C1320" s="3"/>
+      <c r="A1320" s="4">
+        <v>45887</v>
+      </c>
+      <c r="B1320" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1320" s="3">
+        <v>1</v>
+      </c>
       <c r="D1320" s="3"/>
       <c r="E1320" s="3"/>
     </row>
     <row r="1321" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1321" s="4"/>
-      <c r="B1321" s="3"/>
+      <c r="A1321" s="4">
+        <v>45888</v>
+      </c>
+      <c r="B1321" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1321" s="3"/>
       <c r="D1321" s="3"/>
       <c r="E1321" s="3"/>
     </row>
     <row r="1322" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1322" s="4"/>
-      <c r="B1322" s="3"/>
+      <c r="A1322" s="4">
+        <v>45889</v>
+      </c>
+      <c r="B1322" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1322" s="3"/>
       <c r="D1322" s="3"/>
       <c r="E1322" s="3"/>
     </row>
     <row r="1323" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1323" s="4"/>
-      <c r="B1323" s="3"/>
+      <c r="A1323" s="4">
+        <v>45890</v>
+      </c>
+      <c r="B1323" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1323" s="3"/>
       <c r="D1323" s="3"/>
       <c r="E1323" s="3"/>
     </row>
     <row r="1324" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1324" s="4"/>
-      <c r="B1324" s="3"/>
+      <c r="A1324" s="4">
+        <v>45891</v>
+      </c>
+      <c r="B1324" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1324" s="3"/>
-      <c r="D1324" s="3"/>
+      <c r="D1324" s="3">
+        <v>1</v>
+      </c>
       <c r="E1324" s="3"/>
     </row>
     <row r="1325" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1325" s="4"/>
-      <c r="B1325" s="3"/>
-      <c r="C1325" s="3"/>
-      <c r="D1325" s="3"/>
+      <c r="A1325" s="4">
+        <v>45892</v>
+      </c>
+      <c r="B1325" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1325" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1325" s="3">
+        <v>1</v>
+      </c>
       <c r="E1325" s="3"/>
     </row>
     <row r="1326" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1326" s="4"/>
-      <c r="B1326" s="3"/>
-      <c r="C1326" s="3"/>
+      <c r="A1326" s="4">
+        <v>45893</v>
+      </c>
+      <c r="B1326" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1326" s="3">
+        <v>1</v>
+      </c>
       <c r="D1326" s="3"/>
       <c r="E1326" s="3"/>
     </row>
     <row r="1327" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1327" s="4"/>
-      <c r="B1327" s="3"/>
+      <c r="A1327" s="4">
+        <v>45894</v>
+      </c>
+      <c r="B1327" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1327" s="3"/>
       <c r="D1327" s="3"/>
       <c r="E1327" s="3"/>
     </row>
     <row r="1328" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1328" s="4"/>
-      <c r="B1328" s="3"/>
+      <c r="A1328" s="4">
+        <v>45895</v>
+      </c>
+      <c r="B1328" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1328" s="3"/>
       <c r="D1328" s="3"/>
       <c r="E1328" s="3"/>
     </row>
     <row r="1329" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1329" s="4"/>
-      <c r="B1329" s="3"/>
+      <c r="A1329" s="4">
+        <v>45896</v>
+      </c>
+      <c r="B1329" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1329" s="3"/>
       <c r="D1329" s="3"/>
       <c r="E1329" s="3"/>
     </row>
     <row r="1330" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1330" s="4"/>
-      <c r="B1330" s="3"/>
-      <c r="C1330" s="3"/>
+      <c r="A1330" s="4">
+        <v>45897</v>
+      </c>
+      <c r="B1330" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1330" s="3">
+        <v>1</v>
+      </c>
       <c r="D1330" s="3"/>
       <c r="E1330" s="3"/>
     </row>
     <row r="1331" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1331" s="4"/>
-      <c r="B1331" s="3"/>
-      <c r="C1331" s="3"/>
+      <c r="A1331" s="4">
+        <v>45898</v>
+      </c>
+      <c r="B1331" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1331" s="3">
+        <v>1</v>
+      </c>
       <c r="D1331" s="3"/>
       <c r="E1331" s="3"/>
     </row>
     <row r="1332" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1332" s="4"/>
-      <c r="B1332" s="3"/>
-      <c r="C1332" s="3"/>
-      <c r="D1332" s="3"/>
+      <c r="A1332" s="4">
+        <v>45899</v>
+      </c>
+      <c r="B1332" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1332" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1332" s="3">
+        <v>1</v>
+      </c>
       <c r="E1332" s="3"/>
     </row>
     <row r="1333" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1333" s="4"/>
-      <c r="B1333" s="3"/>
-      <c r="C1333" s="3"/>
+      <c r="A1333" s="4">
+        <v>45900</v>
+      </c>
+      <c r="B1333" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1333" s="3">
+        <v>1</v>
+      </c>
       <c r="D1333" s="3"/>
       <c r="E1333" s="3"/>
     </row>
     <row r="1334" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1334" s="4"/>
-      <c r="B1334" s="3"/>
+      <c r="A1334" s="4">
+        <v>45901</v>
+      </c>
+      <c r="B1334" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1334" s="3"/>
       <c r="D1334" s="3"/>
       <c r="E1334" s="3"/>
     </row>
     <row r="1335" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1335" s="4"/>
-      <c r="B1335" s="3"/>
-      <c r="C1335" s="3"/>
+      <c r="A1335" s="4">
+        <v>45902</v>
+      </c>
+      <c r="B1335" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1335" s="3">
+        <v>1</v>
+      </c>
       <c r="D1335" s="3"/>
       <c r="E1335" s="3"/>
     </row>
     <row r="1336" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1336" s="4"/>
-      <c r="B1336" s="3"/>
+      <c r="A1336" s="4">
+        <v>45903</v>
+      </c>
+      <c r="B1336" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C1336" s="3"/>
       <c r="D1336" s="3"/>
       <c r="E1336" s="3"/>
     </row>
     <row r="1337" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1337" s="4"/>
-      <c r="B1337" s="3"/>
+      <c r="A1337" s="4">
+        <v>45904</v>
+      </c>
+      <c r="B1337" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1337" s="3"/>
       <c r="D1337" s="3"/>
       <c r="E1337" s="3"/>
     </row>
     <row r="1338" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1338" s="4"/>
-      <c r="B1338" s="3"/>
+      <c r="A1338" s="4">
+        <v>45905</v>
+      </c>
+      <c r="B1338" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C1338" s="3"/>
       <c r="D1338" s="3"/>
       <c r="E1338" s="3"/>
     </row>
     <row r="1339" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1339" s="4"/>
-      <c r="B1339" s="3"/>
+      <c r="A1339" s="4">
+        <v>45906</v>
+      </c>
+      <c r="B1339" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C1339" s="3"/>
-      <c r="D1339" s="3"/>
+      <c r="D1339" s="3">
+        <v>1</v>
+      </c>
       <c r="E1339" s="3"/>
     </row>
     <row r="1340" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1340" s="4"/>
-      <c r="B1340" s="3"/>
-      <c r="C1340" s="3"/>
+      <c r="A1340" s="4">
+        <v>45907</v>
+      </c>
+      <c r="B1340" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1340" s="3">
+        <v>1</v>
+      </c>
       <c r="D1340" s="3"/>
       <c r="E1340" s="3"/>
     </row>
     <row r="1341" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1341" s="4"/>
-      <c r="B1341" s="3"/>
-      <c r="C1341" s="3"/>
+      <c r="A1341" s="4">
+        <v>45908</v>
+      </c>
+      <c r="B1341" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1341" s="3">
+        <v>1</v>
+      </c>
       <c r="D1341" s="3"/>
       <c r="E1341" s="3"/>
     </row>
     <row r="1342" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1342" s="4"/>
-      <c r="B1342" s="3"/>
+      <c r="A1342" s="4">
+        <v>45909</v>
+      </c>
+      <c r="B1342" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1342" s="3"/>
       <c r="D1342" s="3"/>
       <c r="E1342" s="3"/>
     </row>
     <row r="1343" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1343" s="4"/>
-      <c r="B1343" s="3"/>
-      <c r="C1343" s="3"/>
+      <c r="A1343" s="4">
+        <v>45910</v>
+      </c>
+      <c r="B1343" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1343" s="3">
+        <v>1</v>
+      </c>
       <c r="D1343" s="3"/>
       <c r="E1343" s="3"/>
     </row>
     <row r="1344" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1344" s="4"/>
-      <c r="B1344" s="3"/>
+      <c r="A1344" s="4">
+        <v>45911</v>
+      </c>
+      <c r="B1344" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C1344" s="3"/>
       <c r="D1344" s="3"/>
       <c r="E1344" s="3"/>
     </row>
     <row r="1345" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1345" s="4"/>
-      <c r="B1345" s="3"/>
-      <c r="C1345" s="3"/>
-      <c r="D1345" s="3"/>
+      <c r="A1345" s="4">
+        <v>45912</v>
+      </c>
+      <c r="B1345" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1345" s="3">
+        <v>1</v>
+      </c>
+      <c r="D1345" s="3">
+        <v>1</v>
+      </c>
       <c r="E1345" s="3"/>
     </row>
     <row r="1346" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1346" s="4"/>
-      <c r="B1346" s="3"/>
-      <c r="C1346" s="3"/>
+      <c r="A1346" s="4">
+        <v>45913</v>
+      </c>
+      <c r="B1346" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1346" s="3">
+        <v>1</v>
+      </c>
       <c r="D1346" s="3"/>
       <c r="E1346" s="3"/>
     </row>
     <row r="1347" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1347" s="4"/>
-      <c r="B1347" s="3"/>
+      <c r="A1347" s="4">
+        <v>45914</v>
+      </c>
+      <c r="B1347" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="C1347" s="3"/>
       <c r="D1347" s="3"/>
       <c r="E1347" s="3"/>
     </row>
     <row r="1348" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1348" s="4"/>
-      <c r="B1348" s="3"/>
+      <c r="A1348" s="4">
+        <v>45915</v>
+      </c>
+      <c r="B1348" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C1348" s="3"/>
       <c r="D1348" s="3"/>
       <c r="E1348" s="3"/>
     </row>
     <row r="1349" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1349" s="4"/>
-      <c r="B1349" s="3"/>
+      <c r="A1349" s="4">
+        <v>45916</v>
+      </c>
+      <c r="B1349" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C1349" s="3"/>
       <c r="D1349" s="3"/>
       <c r="E1349" s="3"/>
+    </row>
+    <row r="1350" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1350" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B1350" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1350" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1350" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1351" s="4">
+        <v>45918</v>
+      </c>
+      <c r="B1351" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1351" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1352" s="4">
+        <v>45919</v>
+      </c>
+      <c r="B1352" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1352" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1352" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1353" s="4">
+        <v>45920</v>
+      </c>
+      <c r="B1353" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1353" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1353" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1354" s="4">
+        <v>45921</v>
+      </c>
+      <c r="B1354" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1354" s="7">
+        <v>1</v>
+      </c>
+      <c r="D1354" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1355" s="4">
+        <v>45922</v>
+      </c>
+      <c r="B1355" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1355" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1356" s="4">
+        <v>45923</v>
+      </c>
+      <c r="B1356" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1356" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1357" s="4">
+        <v>45924</v>
+      </c>
+      <c r="B1357" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1357" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1358" s="4">
+        <v>45925</v>
+      </c>
+      <c r="B1358" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1358" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1359" s="4">
+        <v>45926</v>
+      </c>
+      <c r="B1359" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1359" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1359" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1360" s="4">
+        <v>45927</v>
+      </c>
+      <c r="B1360" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1360" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1360" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1361" s="4">
+        <v>45928</v>
+      </c>
+      <c r="B1361" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1361" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1361" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1362" s="4">
+        <v>45929</v>
+      </c>
+      <c r="B1362" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1363" s="4">
+        <v>45930</v>
+      </c>
+      <c r="B1363" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1363" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1364" s="4">
+        <v>45931</v>
+      </c>
+      <c r="B1364" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1364" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1364" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1365" s="4">
+        <v>45932</v>
+      </c>
+      <c r="B1365" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1365" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1366" s="4">
+        <v>45933</v>
+      </c>
+      <c r="B1366" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1366" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1367" s="4">
+        <v>45934</v>
+      </c>
+      <c r="B1367" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1367" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1367" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1368" s="4">
+        <v>45935</v>
+      </c>
+      <c r="B1368" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1368" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1369" s="4">
+        <v>45936</v>
+      </c>
+      <c r="B1369" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1369" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1369" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1370" s="4">
+        <v>45937</v>
+      </c>
+      <c r="B1370" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1370" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1371" s="4">
+        <v>45938</v>
+      </c>
+      <c r="B1371" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1371" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1372" s="4">
+        <v>45939</v>
+      </c>
+      <c r="B1372" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1372" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1373" s="4">
+        <v>45940</v>
+      </c>
+      <c r="B1373" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1373" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1373" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1374" s="4">
+        <v>45941</v>
+      </c>
+      <c r="B1374" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1374" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1374" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1375" s="4">
+        <v>45942</v>
+      </c>
+      <c r="B1375" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1375" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1375" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1376" s="4">
+        <v>45943</v>
+      </c>
+      <c r="B1376" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1376" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1377" s="4">
+        <v>45944</v>
+      </c>
+      <c r="B1377" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1377" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1378" s="4">
+        <v>45945</v>
+      </c>
+      <c r="B1378" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1379" s="4">
+        <v>45946</v>
+      </c>
+      <c r="B1379" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1380" s="4">
+        <v>45947</v>
+      </c>
+      <c r="B1380" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1380" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1381" s="4">
+        <v>45948</v>
+      </c>
+      <c r="B1381" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1381" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1381" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1382" s="4">
+        <v>45949</v>
+      </c>
+      <c r="B1382" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1382" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1383" s="4">
+        <v>45950</v>
+      </c>
+      <c r="B1383" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1383" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1384" s="4">
+        <v>45951</v>
+      </c>
+      <c r="B1384" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1384" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1385" s="4">
+        <v>45952</v>
+      </c>
+      <c r="B1385" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1385" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1385" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1386" s="4">
+        <v>45953</v>
+      </c>
+      <c r="B1386" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1386" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1386" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1387" s="4">
+        <v>45954</v>
+      </c>
+      <c r="B1387" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1387" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1388" s="4">
+        <v>45955</v>
+      </c>
+      <c r="B1388" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1388" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1388" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1389" s="4">
+        <v>45956</v>
+      </c>
+      <c r="B1389" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1389" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1390" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B1390" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1390" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1391" s="4">
+        <v>45958</v>
+      </c>
+      <c r="B1391" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1391" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1392" s="4">
+        <v>45959</v>
+      </c>
+      <c r="B1392" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1392" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1393" s="4">
+        <v>45960</v>
+      </c>
+      <c r="B1393" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1393" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1394" s="4">
+        <v>45961</v>
+      </c>
+      <c r="B1394" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1394" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1394" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1395" s="4">
+        <v>45962</v>
+      </c>
+      <c r="B1395" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1395" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1395" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1396" s="4">
+        <v>45963</v>
+      </c>
+      <c r="B1396" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1396" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1396" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1397" s="4">
+        <v>45964</v>
+      </c>
+      <c r="B1397" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1397" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1398" s="4">
+        <v>45965</v>
+      </c>
+      <c r="B1398" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1399" s="4">
+        <v>45966</v>
+      </c>
+      <c r="B1399" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1400" s="4">
+        <v>45967</v>
+      </c>
+      <c r="B1400" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1400" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1401" s="4">
+        <v>45968</v>
+      </c>
+      <c r="B1401" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1401" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1401" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1402" s="4">
+        <v>45969</v>
+      </c>
+      <c r="B1402" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1402" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1402" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1403" s="4">
+        <v>45970</v>
+      </c>
+      <c r="B1403" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1403" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1404" s="4">
+        <v>45971</v>
+      </c>
+      <c r="B1404" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1404" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1405" s="4">
+        <v>45972</v>
+      </c>
+      <c r="B1405" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1405" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1406" s="4">
+        <v>45973</v>
+      </c>
+      <c r="B1406" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1406" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1406" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1407" s="4">
+        <v>45974</v>
+      </c>
+      <c r="B1407" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1407" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1408" s="4">
+        <v>45975</v>
+      </c>
+      <c r="B1408" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1408" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1408" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1409" s="4">
+        <v>45976</v>
+      </c>
+      <c r="B1409" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1409" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1409" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1410" s="4">
+        <v>45977</v>
+      </c>
+      <c r="B1410" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1410" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1411" s="4">
+        <v>45978</v>
+      </c>
+      <c r="B1411" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1411" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1412" s="4">
+        <v>45979</v>
+      </c>
+      <c r="B1412" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1412" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1412" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1413" s="4">
+        <v>45980</v>
+      </c>
+      <c r="B1413" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1413" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1414" s="4">
+        <v>45981</v>
+      </c>
+      <c r="B1414" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1414" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1415" s="4">
+        <v>45982</v>
+      </c>
+      <c r="B1415" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1415" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1415" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1416" s="4">
+        <v>45983</v>
+      </c>
+      <c r="B1416" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1416" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1416" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1417" s="4">
+        <v>45984</v>
+      </c>
+      <c r="B1417" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1418" s="4">
+        <v>45985</v>
+      </c>
+      <c r="B1418" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1419" s="4">
+        <v>45986</v>
+      </c>
+      <c r="B1419" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1420" s="4">
+        <v>45987</v>
+      </c>
+      <c r="B1420" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1421" s="4">
+        <v>45988</v>
+      </c>
+      <c r="B1421" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1421" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1422" s="4">
+        <v>45989</v>
+      </c>
+      <c r="B1422" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1422" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1422" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1423" s="4">
+        <v>45990</v>
+      </c>
+      <c r="B1423" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1423" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1424" s="4">
+        <v>45991</v>
+      </c>
+      <c r="B1424" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1425" s="4">
+        <v>45992</v>
+      </c>
+      <c r="B1425" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1426" s="4">
+        <v>45993</v>
+      </c>
+      <c r="B1426" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1427" s="4">
+        <v>45994</v>
+      </c>
+      <c r="B1427" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1428" s="4">
+        <v>45995</v>
+      </c>
+      <c r="B1428" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1428" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1429" s="4">
+        <v>45996</v>
+      </c>
+      <c r="B1429" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1429" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1429" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1430" s="4">
+        <v>45997</v>
+      </c>
+      <c r="B1430" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1430" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1431" s="4">
+        <v>45998</v>
+      </c>
+      <c r="B1431" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1431" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1432" s="4">
+        <v>45999</v>
+      </c>
+      <c r="B1432" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1433" s="4">
+        <v>46000</v>
+      </c>
+      <c r="B1433" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1434" s="4">
+        <v>46001</v>
+      </c>
+      <c r="B1434" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1435" s="4">
+        <v>46002</v>
+      </c>
+      <c r="B1435" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1435" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1436" s="4">
+        <v>46003</v>
+      </c>
+      <c r="B1436" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1436" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1436" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1437" s="4">
+        <v>46004</v>
+      </c>
+      <c r="B1437" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1437" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1437" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1438" s="4">
+        <v>46005</v>
+      </c>
+      <c r="B1438" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1438" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1438" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1439" s="4">
+        <v>46006</v>
+      </c>
+      <c r="B1439" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1439" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1439" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1440" s="4">
+        <v>46007</v>
+      </c>
+      <c r="B1440" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1440" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1440" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1441" s="4">
+        <v>46008</v>
+      </c>
+      <c r="B1441" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1441" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1441" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1442" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B1442" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1442" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1442" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1443" s="4">
+        <v>46010</v>
+      </c>
+      <c r="B1443" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1443" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1443" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1444" s="4">
+        <v>46011</v>
+      </c>
+      <c r="B1444" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1444" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1444" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1445" s="4">
+        <v>46012</v>
+      </c>
+      <c r="B1445" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1445" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1445" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1446" s="4">
+        <v>46013</v>
+      </c>
+      <c r="B1446" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1446" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1446" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1447" s="4">
+        <v>46014</v>
+      </c>
+      <c r="B1447" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1447" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1447" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1448" s="4">
+        <v>46015</v>
+      </c>
+      <c r="B1448" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1448" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1448" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1449" s="4">
+        <v>46016</v>
+      </c>
+      <c r="B1449" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1449" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1449" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1450" s="4">
+        <v>46017</v>
+      </c>
+      <c r="B1450" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1450" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1450" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1451" s="4">
+        <v>46018</v>
+      </c>
+      <c r="B1451" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1451" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1451" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1452" s="4">
+        <v>46019</v>
+      </c>
+      <c r="B1452" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1452" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1452" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1453" s="4">
+        <v>46020</v>
+      </c>
+      <c r="B1453" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1453" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1453" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1454" s="4">
+        <v>46021</v>
+      </c>
+      <c r="B1454" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1454" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1454" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1455" s="4">
+        <v>46022</v>
+      </c>
+      <c r="B1455" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1455" s="1">
+        <v>0</v>
+      </c>
+      <c r="D1455" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ongoing_bm/schedule.xlsx
+++ b/ongoing_bm/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Birdman/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B405C8-23F2-1748-98A9-C6C42DC2F9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F87759-18AB-7D48-8E17-25DD6FCAE2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34800" yWindow="3200" windowWidth="29400" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -111,11 +111,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -123,7 +164,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16918,7 +16962,9 @@
       <c r="C1091" s="3">
         <v>1</v>
       </c>
-      <c r="D1091" s="3"/>
+      <c r="D1091" s="3">
+        <v>0</v>
+      </c>
       <c r="E1091" s="3"/>
     </row>
     <row r="1092" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16928,8 +16974,12 @@
       <c r="B1092" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1092" s="3"/>
-      <c r="D1092" s="3"/>
+      <c r="C1092" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1092" s="3">
+        <v>0</v>
+      </c>
       <c r="E1092" s="3"/>
     </row>
     <row r="1093" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16939,8 +16989,12 @@
       <c r="B1093" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1093" s="3"/>
-      <c r="D1093" s="3"/>
+      <c r="C1093" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1093" s="3">
+        <v>0</v>
+      </c>
       <c r="E1093" s="3"/>
     </row>
     <row r="1094" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16950,8 +17004,12 @@
       <c r="B1094" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1094" s="3"/>
-      <c r="D1094" s="3"/>
+      <c r="C1094" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1094" s="3">
+        <v>0</v>
+      </c>
       <c r="E1094" s="3"/>
     </row>
     <row r="1095" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16961,8 +17019,12 @@
       <c r="B1095" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1095" s="3"/>
-      <c r="D1095" s="3"/>
+      <c r="C1095" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1095" s="3">
+        <v>0</v>
+      </c>
       <c r="E1095" s="3"/>
     </row>
     <row r="1096" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16975,7 +17037,9 @@
       <c r="C1096" s="3">
         <v>1</v>
       </c>
-      <c r="D1096" s="3"/>
+      <c r="D1096" s="3">
+        <v>0</v>
+      </c>
       <c r="E1096" s="3"/>
     </row>
     <row r="1097" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16988,7 +17052,9 @@
       <c r="C1097" s="3">
         <v>1</v>
       </c>
-      <c r="D1097" s="3"/>
+      <c r="D1097" s="3">
+        <v>0</v>
+      </c>
       <c r="E1097" s="3"/>
     </row>
     <row r="1098" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -16998,8 +17064,12 @@
       <c r="B1098" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1098" s="3"/>
-      <c r="D1098" s="3"/>
+      <c r="C1098" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1098" s="3">
+        <v>0</v>
+      </c>
       <c r="E1098" s="3"/>
     </row>
     <row r="1099" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17012,7 +17082,9 @@
       <c r="C1099" s="3">
         <v>1</v>
       </c>
-      <c r="D1099" s="3"/>
+      <c r="D1099" s="3">
+        <v>0</v>
+      </c>
       <c r="E1099" s="3"/>
     </row>
     <row r="1100" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17025,7 +17097,9 @@
       <c r="C1100" s="3">
         <v>1</v>
       </c>
-      <c r="D1100" s="3"/>
+      <c r="D1100" s="3">
+        <v>0</v>
+      </c>
       <c r="E1100" s="3"/>
     </row>
     <row r="1101" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17035,8 +17109,12 @@
       <c r="B1101" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1101" s="3"/>
-      <c r="D1101" s="3"/>
+      <c r="C1101" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1101" s="3">
+        <v>0</v>
+      </c>
       <c r="E1101" s="3"/>
     </row>
     <row r="1102" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17046,8 +17124,12 @@
       <c r="B1102" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1102" s="3"/>
-      <c r="D1102" s="3"/>
+      <c r="C1102" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1102" s="3">
+        <v>0</v>
+      </c>
       <c r="E1102" s="3"/>
     </row>
     <row r="1103" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17060,7 +17142,9 @@
       <c r="C1103" s="3">
         <v>1</v>
       </c>
-      <c r="D1103" s="3"/>
+      <c r="D1103" s="3">
+        <v>0</v>
+      </c>
       <c r="E1103" s="3"/>
     </row>
     <row r="1104" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17073,7 +17157,9 @@
       <c r="C1104" s="3">
         <v>1</v>
       </c>
-      <c r="D1104" s="3"/>
+      <c r="D1104" s="3">
+        <v>0</v>
+      </c>
       <c r="E1104" s="3"/>
     </row>
     <row r="1105" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17083,8 +17169,12 @@
       <c r="B1105" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1105" s="3"/>
-      <c r="D1105" s="3"/>
+      <c r="C1105" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1105" s="3">
+        <v>0</v>
+      </c>
       <c r="E1105" s="3"/>
     </row>
     <row r="1106" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17097,7 +17187,9 @@
       <c r="C1106" s="3">
         <v>1</v>
       </c>
-      <c r="D1106" s="3"/>
+      <c r="D1106" s="3">
+        <v>0</v>
+      </c>
       <c r="E1106" s="3"/>
     </row>
     <row r="1107" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17107,8 +17199,12 @@
       <c r="B1107" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1107" s="3"/>
-      <c r="D1107" s="3"/>
+      <c r="C1107" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1107" s="3">
+        <v>0</v>
+      </c>
       <c r="E1107" s="3"/>
     </row>
     <row r="1108" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17121,7 +17217,9 @@
       <c r="C1108" s="3">
         <v>1</v>
       </c>
-      <c r="D1108" s="3"/>
+      <c r="D1108" s="3">
+        <v>0</v>
+      </c>
       <c r="E1108" s="3"/>
     </row>
     <row r="1109" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17131,8 +17229,12 @@
       <c r="B1109" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1109" s="3"/>
-      <c r="D1109" s="3"/>
+      <c r="C1109" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1109" s="3">
+        <v>0</v>
+      </c>
       <c r="E1109" s="3"/>
     </row>
     <row r="1110" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17145,7 +17247,9 @@
       <c r="C1110" s="3">
         <v>1</v>
       </c>
-      <c r="D1110" s="3"/>
+      <c r="D1110" s="3">
+        <v>0</v>
+      </c>
       <c r="E1110" s="3"/>
     </row>
     <row r="1111" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17155,8 +17259,12 @@
       <c r="B1111" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1111" s="3"/>
-      <c r="D1111" s="3"/>
+      <c r="C1111" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1111" s="3">
+        <v>0</v>
+      </c>
       <c r="E1111" s="3"/>
     </row>
     <row r="1112" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17169,7 +17277,9 @@
       <c r="C1112" s="3">
         <v>1</v>
       </c>
-      <c r="D1112" s="3"/>
+      <c r="D1112" s="3">
+        <v>0</v>
+      </c>
       <c r="E1112" s="3"/>
     </row>
     <row r="1113" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17179,8 +17289,12 @@
       <c r="B1113" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1113" s="3"/>
-      <c r="D1113" s="3"/>
+      <c r="C1113" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1113" s="3">
+        <v>0</v>
+      </c>
       <c r="E1113" s="3"/>
     </row>
     <row r="1114" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17193,7 +17307,9 @@
       <c r="C1114" s="3">
         <v>1</v>
       </c>
-      <c r="D1114" s="3"/>
+      <c r="D1114" s="3">
+        <v>0</v>
+      </c>
       <c r="E1114" s="3"/>
     </row>
     <row r="1115" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17203,8 +17319,12 @@
       <c r="B1115" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1115" s="3"/>
-      <c r="D1115" s="3"/>
+      <c r="C1115" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1115" s="3">
+        <v>0</v>
+      </c>
       <c r="E1115" s="3"/>
     </row>
     <row r="1116" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17217,7 +17337,9 @@
       <c r="C1116" s="3">
         <v>1</v>
       </c>
-      <c r="D1116" s="3"/>
+      <c r="D1116" s="3">
+        <v>0</v>
+      </c>
       <c r="E1116" s="3"/>
     </row>
     <row r="1117" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17227,8 +17349,12 @@
       <c r="B1117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1117" s="3"/>
-      <c r="D1117" s="3"/>
+      <c r="C1117" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1117" s="3">
+        <v>0</v>
+      </c>
       <c r="E1117" s="3"/>
     </row>
     <row r="1118" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17241,7 +17367,9 @@
       <c r="C1118" s="3">
         <v>1</v>
       </c>
-      <c r="D1118" s="3"/>
+      <c r="D1118" s="3">
+        <v>0</v>
+      </c>
       <c r="E1118" s="3"/>
     </row>
     <row r="1119" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17254,7 +17382,9 @@
       <c r="C1119" s="3">
         <v>1</v>
       </c>
-      <c r="D1119" s="3"/>
+      <c r="D1119" s="3">
+        <v>0</v>
+      </c>
       <c r="E1119" s="3"/>
     </row>
     <row r="1120" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17264,8 +17394,12 @@
       <c r="B1120" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1120" s="3"/>
-      <c r="D1120" s="3"/>
+      <c r="C1120" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1120" s="3">
+        <v>0</v>
+      </c>
       <c r="E1120" s="3"/>
     </row>
     <row r="1121" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17293,7 +17427,9 @@
       <c r="C1122" s="3">
         <v>1</v>
       </c>
-      <c r="D1122" s="3"/>
+      <c r="D1122" s="3">
+        <v>0</v>
+      </c>
       <c r="E1122" s="3"/>
     </row>
     <row r="1123" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17306,7 +17442,9 @@
       <c r="C1123" s="3">
         <v>1</v>
       </c>
-      <c r="D1123" s="3"/>
+      <c r="D1123" s="3">
+        <v>0</v>
+      </c>
       <c r="E1123" s="3"/>
     </row>
     <row r="1124" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17316,8 +17454,12 @@
       <c r="B1124" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1124" s="3"/>
-      <c r="D1124" s="3"/>
+      <c r="C1124" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1124" s="3">
+        <v>0</v>
+      </c>
       <c r="E1124" s="3"/>
     </row>
     <row r="1125" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17327,8 +17469,12 @@
       <c r="B1125" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1125" s="3"/>
-      <c r="D1125" s="3"/>
+      <c r="C1125" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1125" s="3">
+        <v>0</v>
+      </c>
       <c r="E1125" s="3"/>
     </row>
     <row r="1126" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17338,8 +17484,12 @@
       <c r="B1126" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1126" s="3"/>
-      <c r="D1126" s="3"/>
+      <c r="C1126" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1126" s="3">
+        <v>0</v>
+      </c>
       <c r="E1126" s="3"/>
     </row>
     <row r="1127" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17349,8 +17499,12 @@
       <c r="B1127" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1127" s="3"/>
-      <c r="D1127" s="3"/>
+      <c r="C1127" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1127" s="3">
+        <v>0</v>
+      </c>
       <c r="E1127" s="3"/>
     </row>
     <row r="1128" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17360,7 +17514,9 @@
       <c r="B1128" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1128" s="3"/>
+      <c r="C1128" s="3">
+        <v>0</v>
+      </c>
       <c r="D1128" s="3">
         <v>1</v>
       </c>
@@ -17403,8 +17559,12 @@
       <c r="B1131" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1131" s="3"/>
-      <c r="D1131" s="3"/>
+      <c r="C1131" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1131" s="3">
+        <v>0</v>
+      </c>
       <c r="E1131" s="3"/>
     </row>
     <row r="1132" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17417,7 +17577,9 @@
       <c r="C1132" s="3">
         <v>1</v>
       </c>
-      <c r="D1132" s="3"/>
+      <c r="D1132" s="3">
+        <v>0</v>
+      </c>
       <c r="E1132" s="3"/>
     </row>
     <row r="1133" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17427,8 +17589,12 @@
       <c r="B1133" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1133" s="3"/>
-      <c r="D1133" s="3"/>
+      <c r="C1133" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1133" s="3">
+        <v>0</v>
+      </c>
       <c r="E1133" s="3"/>
     </row>
     <row r="1134" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17438,8 +17604,12 @@
       <c r="B1134" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1134" s="3"/>
-      <c r="D1134" s="3"/>
+      <c r="C1134" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1134" s="3">
+        <v>0</v>
+      </c>
       <c r="E1134" s="3"/>
     </row>
     <row r="1135" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17449,7 +17619,9 @@
       <c r="B1135" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1135" s="3"/>
+      <c r="C1135" s="3">
+        <v>0</v>
+      </c>
       <c r="D1135" s="3">
         <v>1</v>
       </c>
@@ -17480,7 +17652,9 @@
       <c r="C1137" s="3">
         <v>1</v>
       </c>
-      <c r="D1137" s="3"/>
+      <c r="D1137" s="3">
+        <v>0</v>
+      </c>
       <c r="E1137" s="3"/>
     </row>
     <row r="1138" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17490,8 +17664,12 @@
       <c r="B1138" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1138" s="3"/>
-      <c r="D1138" s="3"/>
+      <c r="C1138" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1138" s="3">
+        <v>0</v>
+      </c>
       <c r="E1138" s="3"/>
     </row>
     <row r="1139" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17501,8 +17679,12 @@
       <c r="B1139" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1139" s="3"/>
-      <c r="D1139" s="3"/>
+      <c r="C1139" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1139" s="3">
+        <v>0</v>
+      </c>
       <c r="E1139" s="3"/>
     </row>
     <row r="1140" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17512,8 +17694,12 @@
       <c r="B1140" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1140" s="3"/>
-      <c r="D1140" s="3"/>
+      <c r="C1140" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1140" s="3">
+        <v>0</v>
+      </c>
       <c r="E1140" s="3"/>
     </row>
     <row r="1141" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17526,7 +17712,9 @@
       <c r="C1141" s="3">
         <v>1</v>
       </c>
-      <c r="D1141" s="3"/>
+      <c r="D1141" s="3">
+        <v>0</v>
+      </c>
       <c r="E1141" s="3"/>
     </row>
     <row r="1142" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17566,8 +17754,12 @@
       <c r="B1144" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1144" s="3"/>
-      <c r="D1144" s="3"/>
+      <c r="C1144" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1144" s="3">
+        <v>0</v>
+      </c>
       <c r="E1144" s="3"/>
     </row>
     <row r="1145" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17580,7 +17772,9 @@
       <c r="C1145" s="3">
         <v>1</v>
       </c>
-      <c r="D1145" s="3"/>
+      <c r="D1145" s="3">
+        <v>0</v>
+      </c>
       <c r="E1145" s="3"/>
     </row>
     <row r="1146" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17590,8 +17784,12 @@
       <c r="B1146" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1146" s="3"/>
-      <c r="D1146" s="3"/>
+      <c r="C1146" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1146" s="3">
+        <v>0</v>
+      </c>
       <c r="E1146" s="3"/>
     </row>
     <row r="1147" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17601,8 +17799,12 @@
       <c r="B1147" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1147" s="3"/>
-      <c r="D1147" s="3"/>
+      <c r="C1147" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1147" s="3">
+        <v>0</v>
+      </c>
       <c r="E1147" s="3"/>
     </row>
     <row r="1148" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17612,8 +17814,12 @@
       <c r="B1148" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1148" s="3"/>
-      <c r="D1148" s="3"/>
+      <c r="C1148" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1148" s="3">
+        <v>0</v>
+      </c>
       <c r="E1148" s="3"/>
     </row>
     <row r="1149" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17623,7 +17829,9 @@
       <c r="B1149" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1149" s="3"/>
+      <c r="C1149" s="3">
+        <v>0</v>
+      </c>
       <c r="D1149" s="3">
         <v>1</v>
       </c>
@@ -17654,7 +17862,9 @@
       <c r="C1151" s="3">
         <v>1</v>
       </c>
-      <c r="D1151" s="3"/>
+      <c r="D1151" s="3">
+        <v>0</v>
+      </c>
       <c r="E1151" s="3"/>
     </row>
     <row r="1152" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17664,8 +17874,12 @@
       <c r="B1152" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1152" s="3"/>
-      <c r="D1152" s="3"/>
+      <c r="C1152" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1152" s="3">
+        <v>0</v>
+      </c>
       <c r="E1152" s="3"/>
     </row>
     <row r="1153" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17675,8 +17889,12 @@
       <c r="B1153" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1153" s="3"/>
-      <c r="D1153" s="3"/>
+      <c r="C1153" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1153" s="3">
+        <v>0</v>
+      </c>
       <c r="E1153" s="3"/>
     </row>
     <row r="1154" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17686,8 +17904,12 @@
       <c r="B1154" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1154" s="3"/>
-      <c r="D1154" s="3"/>
+      <c r="C1154" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1154" s="3">
+        <v>0</v>
+      </c>
       <c r="E1154" s="3"/>
     </row>
     <row r="1155" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17700,7 +17922,9 @@
       <c r="C1155" s="3">
         <v>1</v>
       </c>
-      <c r="D1155" s="3"/>
+      <c r="D1155" s="3">
+        <v>0</v>
+      </c>
       <c r="E1155" s="3"/>
     </row>
     <row r="1156" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17740,8 +17964,12 @@
       <c r="B1158" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1158" s="3"/>
-      <c r="D1158" s="3"/>
+      <c r="C1158" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1158" s="3">
+        <v>0</v>
+      </c>
       <c r="E1158" s="3"/>
     </row>
     <row r="1159" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17751,8 +17979,12 @@
       <c r="B1159" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1159" s="3"/>
-      <c r="D1159" s="3"/>
+      <c r="C1159" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1159" s="3">
+        <v>0</v>
+      </c>
       <c r="E1159" s="3"/>
     </row>
     <row r="1160" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17765,7 +17997,9 @@
       <c r="C1160" s="3">
         <v>1</v>
       </c>
-      <c r="D1160" s="3"/>
+      <c r="D1160" s="3">
+        <v>0</v>
+      </c>
       <c r="E1160" s="3"/>
     </row>
     <row r="1161" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17778,7 +18012,9 @@
       <c r="C1161" s="3">
         <v>1</v>
       </c>
-      <c r="D1161" s="3"/>
+      <c r="D1161" s="3">
+        <v>0</v>
+      </c>
       <c r="E1161" s="3"/>
     </row>
     <row r="1162" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17788,8 +18024,12 @@
       <c r="B1162" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1162" s="3"/>
-      <c r="D1162" s="3"/>
+      <c r="C1162" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1162" s="3">
+        <v>0</v>
+      </c>
       <c r="E1162" s="3"/>
     </row>
     <row r="1163" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17829,8 +18069,12 @@
       <c r="B1165" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1165" s="3"/>
-      <c r="D1165" s="3"/>
+      <c r="C1165" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1165" s="3">
+        <v>0</v>
+      </c>
       <c r="E1165" s="3"/>
     </row>
     <row r="1166" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17843,7 +18087,9 @@
       <c r="C1166" s="3">
         <v>1</v>
       </c>
-      <c r="D1166" s="3"/>
+      <c r="D1166" s="3">
+        <v>0</v>
+      </c>
       <c r="E1166" s="3"/>
     </row>
     <row r="1167" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17853,8 +18099,12 @@
       <c r="B1167" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1167" s="3"/>
-      <c r="D1167" s="3"/>
+      <c r="C1167" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1167" s="3">
+        <v>0</v>
+      </c>
       <c r="E1167" s="3"/>
     </row>
     <row r="1168" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17867,7 +18117,9 @@
       <c r="C1168" s="3">
         <v>1</v>
       </c>
-      <c r="D1168" s="3"/>
+      <c r="D1168" s="3">
+        <v>0</v>
+      </c>
       <c r="E1168" s="3"/>
     </row>
     <row r="1169" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17877,8 +18129,12 @@
       <c r="B1169" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1169" s="3"/>
-      <c r="D1169" s="3"/>
+      <c r="C1169" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1169" s="3">
+        <v>0</v>
+      </c>
       <c r="E1169" s="3"/>
     </row>
     <row r="1170" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17921,7 +18177,9 @@
       <c r="C1172" s="3">
         <v>1</v>
       </c>
-      <c r="D1172" s="3"/>
+      <c r="D1172" s="3">
+        <v>0</v>
+      </c>
       <c r="E1172" s="3"/>
     </row>
     <row r="1173" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17931,8 +18189,12 @@
       <c r="B1173" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1173" s="3"/>
-      <c r="D1173" s="3"/>
+      <c r="C1173" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1173" s="3">
+        <v>0</v>
+      </c>
       <c r="E1173" s="3"/>
     </row>
     <row r="1174" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17942,8 +18204,12 @@
       <c r="B1174" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1174" s="3"/>
-      <c r="D1174" s="3"/>
+      <c r="C1174" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1174" s="3">
+        <v>0</v>
+      </c>
       <c r="E1174" s="3"/>
     </row>
     <row r="1175" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17953,8 +18219,12 @@
       <c r="B1175" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1175" s="3"/>
-      <c r="D1175" s="3"/>
+      <c r="C1175" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1175" s="3">
+        <v>0</v>
+      </c>
       <c r="E1175" s="3"/>
     </row>
     <row r="1176" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17964,8 +18234,12 @@
       <c r="B1176" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1176" s="3"/>
-      <c r="D1176" s="3"/>
+      <c r="C1176" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1176" s="3">
+        <v>0</v>
+      </c>
       <c r="E1176" s="3"/>
     </row>
     <row r="1177" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -17978,7 +18252,9 @@
       <c r="C1177" s="3">
         <v>1</v>
       </c>
-      <c r="D1177" s="3"/>
+      <c r="D1177" s="3">
+        <v>0</v>
+      </c>
       <c r="E1177" s="3"/>
     </row>
     <row r="1178" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18006,7 +18282,9 @@
       <c r="C1179" s="3">
         <v>1</v>
       </c>
-      <c r="D1179" s="3"/>
+      <c r="D1179" s="3">
+        <v>0</v>
+      </c>
       <c r="E1179" s="3"/>
     </row>
     <row r="1180" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18019,7 +18297,9 @@
       <c r="C1180" s="3">
         <v>1</v>
       </c>
-      <c r="D1180" s="3"/>
+      <c r="D1180" s="3">
+        <v>0</v>
+      </c>
       <c r="E1180" s="3"/>
     </row>
     <row r="1181" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18029,8 +18309,12 @@
       <c r="B1181" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1181" s="3"/>
-      <c r="D1181" s="3"/>
+      <c r="C1181" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1181" s="3">
+        <v>0</v>
+      </c>
       <c r="E1181" s="3"/>
     </row>
     <row r="1182" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18040,8 +18324,12 @@
       <c r="B1182" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1182" s="3"/>
-      <c r="D1182" s="3"/>
+      <c r="C1182" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1182" s="3">
+        <v>0</v>
+      </c>
       <c r="E1182" s="3"/>
     </row>
     <row r="1183" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18051,8 +18339,12 @@
       <c r="B1183" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1183" s="3"/>
-      <c r="D1183" s="3"/>
+      <c r="C1183" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1183" s="3">
+        <v>0</v>
+      </c>
       <c r="E1183" s="3"/>
     </row>
     <row r="1184" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18095,7 +18387,9 @@
       <c r="C1186" s="3">
         <v>1</v>
       </c>
-      <c r="D1186" s="3"/>
+      <c r="D1186" s="3">
+        <v>0</v>
+      </c>
       <c r="E1186" s="3"/>
     </row>
     <row r="1187" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18105,8 +18399,12 @@
       <c r="B1187" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1187" s="3"/>
-      <c r="D1187" s="3"/>
+      <c r="C1187" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1187" s="3">
+        <v>0</v>
+      </c>
       <c r="E1187" s="3"/>
     </row>
     <row r="1188" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18116,8 +18414,12 @@
       <c r="B1188" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1188" s="3"/>
-      <c r="D1188" s="3"/>
+      <c r="C1188" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1188" s="3">
+        <v>0</v>
+      </c>
       <c r="E1188" s="3"/>
     </row>
     <row r="1189" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18127,8 +18429,12 @@
       <c r="B1189" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1189" s="3"/>
-      <c r="D1189" s="3"/>
+      <c r="C1189" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1189" s="3">
+        <v>0</v>
+      </c>
       <c r="E1189" s="3"/>
     </row>
     <row r="1190" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18141,7 +18447,9 @@
       <c r="C1190" s="3">
         <v>1</v>
       </c>
-      <c r="D1190" s="3"/>
+      <c r="D1190" s="3">
+        <v>0</v>
+      </c>
       <c r="E1190" s="3"/>
     </row>
     <row r="1191" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18184,7 +18492,9 @@
       <c r="C1193" s="3">
         <v>1</v>
       </c>
-      <c r="D1193" s="3"/>
+      <c r="D1193" s="3">
+        <v>0</v>
+      </c>
       <c r="E1193" s="3"/>
     </row>
     <row r="1194" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18194,8 +18504,12 @@
       <c r="B1194" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1194" s="3"/>
-      <c r="D1194" s="3"/>
+      <c r="C1194" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1194" s="3">
+        <v>0</v>
+      </c>
       <c r="E1194" s="3"/>
     </row>
     <row r="1195" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18205,8 +18519,12 @@
       <c r="B1195" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1195" s="3"/>
-      <c r="D1195" s="3"/>
+      <c r="C1195" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1195" s="3">
+        <v>0</v>
+      </c>
       <c r="E1195" s="3"/>
     </row>
     <row r="1196" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18216,8 +18534,12 @@
       <c r="B1196" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1196" s="3"/>
-      <c r="D1196" s="3"/>
+      <c r="C1196" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1196" s="3">
+        <v>0</v>
+      </c>
       <c r="E1196" s="3"/>
     </row>
     <row r="1197" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18227,7 +18549,9 @@
       <c r="B1197" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1197" s="3"/>
+      <c r="C1197" s="3">
+        <v>0</v>
+      </c>
       <c r="D1197" s="3">
         <v>1</v>
       </c>
@@ -18243,7 +18567,9 @@
       <c r="C1198" s="3">
         <v>1</v>
       </c>
-      <c r="D1198" s="3"/>
+      <c r="D1198" s="3">
+        <v>0</v>
+      </c>
       <c r="E1198" s="3"/>
     </row>
     <row r="1199" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18271,7 +18597,9 @@
       <c r="C1200" s="3">
         <v>1</v>
       </c>
-      <c r="D1200" s="3"/>
+      <c r="D1200" s="3">
+        <v>0</v>
+      </c>
       <c r="E1200" s="3"/>
     </row>
     <row r="1201" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18284,7 +18612,9 @@
       <c r="C1201" s="3">
         <v>1</v>
       </c>
-      <c r="D1201" s="3"/>
+      <c r="D1201" s="3">
+        <v>0</v>
+      </c>
       <c r="E1201" s="3"/>
     </row>
     <row r="1202" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18294,8 +18624,12 @@
       <c r="B1202" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1202" s="3"/>
-      <c r="D1202" s="3"/>
+      <c r="C1202" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1202" s="3">
+        <v>0</v>
+      </c>
       <c r="E1202" s="3"/>
     </row>
     <row r="1203" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18308,7 +18642,9 @@
       <c r="C1203" s="3">
         <v>1</v>
       </c>
-      <c r="D1203" s="3"/>
+      <c r="D1203" s="3">
+        <v>0</v>
+      </c>
       <c r="E1203" s="3"/>
     </row>
     <row r="1204" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18318,7 +18654,9 @@
       <c r="B1204" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1204" s="3"/>
+      <c r="C1204" s="3">
+        <v>0</v>
+      </c>
       <c r="D1204" s="3">
         <v>1</v>
       </c>
@@ -18334,7 +18672,9 @@
       <c r="C1205" s="3">
         <v>1</v>
       </c>
-      <c r="D1205" s="3"/>
+      <c r="D1205" s="3">
+        <v>0</v>
+      </c>
       <c r="E1205" s="3"/>
     </row>
     <row r="1206" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18344,7 +18684,9 @@
       <c r="B1206" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1206" s="3"/>
+      <c r="C1206" s="3">
+        <v>0</v>
+      </c>
       <c r="D1206" s="3">
         <v>1</v>
       </c>
@@ -18360,7 +18702,9 @@
       <c r="C1207" s="3">
         <v>1</v>
       </c>
-      <c r="D1207" s="3"/>
+      <c r="D1207" s="3">
+        <v>0</v>
+      </c>
       <c r="E1207" s="3"/>
     </row>
     <row r="1208" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18373,7 +18717,9 @@
       <c r="C1208" s="3">
         <v>1</v>
       </c>
-      <c r="D1208" s="3"/>
+      <c r="D1208" s="3">
+        <v>0</v>
+      </c>
       <c r="E1208" s="3"/>
     </row>
     <row r="1209" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18383,8 +18729,12 @@
       <c r="B1209" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1209" s="3"/>
-      <c r="D1209" s="3"/>
+      <c r="C1209" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1209" s="3">
+        <v>0</v>
+      </c>
       <c r="E1209" s="3"/>
     </row>
     <row r="1210" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18394,8 +18744,12 @@
       <c r="B1210" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1210" s="3"/>
-      <c r="D1210" s="3"/>
+      <c r="C1210" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1210" s="3">
+        <v>0</v>
+      </c>
       <c r="E1210" s="3"/>
     </row>
     <row r="1211" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18405,7 +18759,9 @@
       <c r="B1211" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1211" s="3"/>
+      <c r="C1211" s="3">
+        <v>0</v>
+      </c>
       <c r="D1211" s="3">
         <v>1</v>
       </c>
@@ -18421,7 +18777,9 @@
       <c r="C1212" s="3">
         <v>1</v>
       </c>
-      <c r="D1212" s="3"/>
+      <c r="D1212" s="3">
+        <v>0</v>
+      </c>
       <c r="E1212" s="3"/>
     </row>
     <row r="1213" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18449,7 +18807,9 @@
       <c r="C1214" s="3">
         <v>1</v>
       </c>
-      <c r="D1214" s="3"/>
+      <c r="D1214" s="3">
+        <v>0</v>
+      </c>
       <c r="E1214" s="3"/>
     </row>
     <row r="1215" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18489,7 +18849,9 @@
       <c r="B1217" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1217" s="3"/>
+      <c r="C1217" s="3">
+        <v>0</v>
+      </c>
       <c r="D1217" s="3">
         <v>1</v>
       </c>
@@ -18502,7 +18864,9 @@
       <c r="B1218" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1218" s="3"/>
+      <c r="C1218" s="3">
+        <v>0</v>
+      </c>
       <c r="D1218" s="3">
         <v>1</v>
       </c>
@@ -18515,8 +18879,12 @@
       <c r="B1219" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1219" s="3"/>
-      <c r="D1219" s="3"/>
+      <c r="C1219" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1219" s="3">
+        <v>0</v>
+      </c>
       <c r="E1219" s="3"/>
     </row>
     <row r="1220" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18526,7 +18894,9 @@
       <c r="B1220" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1220" s="3"/>
+      <c r="C1220" s="3">
+        <v>0</v>
+      </c>
       <c r="D1220" s="3">
         <v>1</v>
       </c>
@@ -18542,7 +18912,9 @@
       <c r="C1221" s="3">
         <v>1</v>
       </c>
-      <c r="D1221" s="3"/>
+      <c r="D1221" s="3">
+        <v>0</v>
+      </c>
       <c r="E1221" s="3"/>
     </row>
     <row r="1222" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18552,8 +18924,12 @@
       <c r="B1222" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1222" s="3"/>
-      <c r="D1222" s="3"/>
+      <c r="C1222" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1222" s="3">
+        <v>0</v>
+      </c>
       <c r="E1222" s="3"/>
     </row>
     <row r="1223" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18566,7 +18942,9 @@
       <c r="C1223" s="3">
         <v>1</v>
       </c>
-      <c r="D1223" s="3"/>
+      <c r="D1223" s="3">
+        <v>0</v>
+      </c>
       <c r="E1223" s="3"/>
     </row>
     <row r="1224" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18576,8 +18954,12 @@
       <c r="B1224" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1224" s="3"/>
-      <c r="D1224" s="3"/>
+      <c r="C1224" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1224" s="3">
+        <v>0</v>
+      </c>
       <c r="E1224" s="3"/>
     </row>
     <row r="1225" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18587,8 +18969,12 @@
       <c r="B1225" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1225" s="3"/>
-      <c r="D1225" s="3"/>
+      <c r="C1225" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1225" s="3">
+        <v>0</v>
+      </c>
       <c r="E1225" s="3"/>
     </row>
     <row r="1226" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18631,7 +19017,9 @@
       <c r="C1228" s="3">
         <v>1</v>
       </c>
-      <c r="D1228" s="3"/>
+      <c r="D1228" s="3">
+        <v>0</v>
+      </c>
       <c r="E1228" s="3"/>
     </row>
     <row r="1229" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18641,8 +19029,12 @@
       <c r="B1229" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1229" s="3"/>
-      <c r="D1229" s="3"/>
+      <c r="C1229" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1229" s="3">
+        <v>0</v>
+      </c>
       <c r="E1229" s="3"/>
     </row>
     <row r="1230" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18652,8 +19044,12 @@
       <c r="B1230" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1230" s="3"/>
-      <c r="D1230" s="3"/>
+      <c r="C1230" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1230" s="3">
+        <v>0</v>
+      </c>
       <c r="E1230" s="3"/>
     </row>
     <row r="1231" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18663,8 +19059,12 @@
       <c r="B1231" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1231" s="3"/>
-      <c r="D1231" s="3"/>
+      <c r="C1231" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1231" s="3">
+        <v>0</v>
+      </c>
       <c r="E1231" s="3"/>
     </row>
     <row r="1232" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18674,7 +19074,9 @@
       <c r="B1232" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1232" s="3"/>
+      <c r="C1232" s="3">
+        <v>0</v>
+      </c>
       <c r="D1232" s="3">
         <v>1</v>
       </c>
@@ -18720,7 +19122,9 @@
       <c r="C1235" s="3">
         <v>1</v>
       </c>
-      <c r="D1235" s="3"/>
+      <c r="D1235" s="3">
+        <v>0</v>
+      </c>
       <c r="E1235" s="3"/>
     </row>
     <row r="1236" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18730,8 +19134,12 @@
       <c r="B1236" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1236" s="3"/>
-      <c r="D1236" s="3"/>
+      <c r="C1236" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1236" s="3">
+        <v>0</v>
+      </c>
       <c r="E1236" s="3"/>
     </row>
     <row r="1237" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18741,7 +19149,9 @@
       <c r="B1237" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1237" s="3"/>
+      <c r="C1237" s="3">
+        <v>0</v>
+      </c>
       <c r="D1237" s="3">
         <v>1</v>
       </c>
@@ -18757,7 +19167,9 @@
       <c r="C1238" s="3">
         <v>1</v>
       </c>
-      <c r="D1238" s="3"/>
+      <c r="D1238" s="3">
+        <v>0</v>
+      </c>
       <c r="E1238" s="3"/>
     </row>
     <row r="1239" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18767,8 +19179,12 @@
       <c r="B1239" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1239" s="3"/>
-      <c r="D1239" s="3"/>
+      <c r="C1239" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1239" s="3">
+        <v>0</v>
+      </c>
       <c r="E1239" s="3"/>
     </row>
     <row r="1240" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18778,7 +19194,9 @@
       <c r="B1240" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1240" s="3"/>
+      <c r="C1240" s="3">
+        <v>0</v>
+      </c>
       <c r="D1240" s="3">
         <v>1</v>
       </c>
@@ -18791,7 +19209,9 @@
       <c r="B1241" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1241" s="3"/>
+      <c r="C1241" s="3">
+        <v>0</v>
+      </c>
       <c r="D1241" s="3">
         <v>1</v>
       </c>
@@ -18807,7 +19227,9 @@
       <c r="C1242" s="3">
         <v>1</v>
       </c>
-      <c r="D1242" s="3"/>
+      <c r="D1242" s="3">
+        <v>0</v>
+      </c>
       <c r="E1242" s="3"/>
     </row>
     <row r="1243" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18820,7 +19242,9 @@
       <c r="C1243" s="3">
         <v>1</v>
       </c>
-      <c r="D1243" s="3"/>
+      <c r="D1243" s="3">
+        <v>0</v>
+      </c>
       <c r="E1243" s="3"/>
     </row>
     <row r="1244" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18830,8 +19254,12 @@
       <c r="B1244" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1244" s="3"/>
-      <c r="D1244" s="3"/>
+      <c r="C1244" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1244" s="3">
+        <v>0</v>
+      </c>
       <c r="E1244" s="3"/>
     </row>
     <row r="1245" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18841,8 +19269,12 @@
       <c r="B1245" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1245" s="3"/>
-      <c r="D1245" s="3"/>
+      <c r="C1245" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1245" s="3">
+        <v>0</v>
+      </c>
       <c r="E1245" s="3"/>
     </row>
     <row r="1246" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18852,8 +19284,12 @@
       <c r="B1246" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1246" s="3"/>
-      <c r="D1246" s="3"/>
+      <c r="C1246" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1246" s="3">
+        <v>0</v>
+      </c>
       <c r="E1246" s="3"/>
     </row>
     <row r="1247" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18893,8 +19329,12 @@
       <c r="B1249" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1249" s="3"/>
-      <c r="D1249" s="3"/>
+      <c r="C1249" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1249" s="3">
+        <v>0</v>
+      </c>
       <c r="E1249" s="3"/>
     </row>
     <row r="1250" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18904,8 +19344,12 @@
       <c r="B1250" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1250" s="3"/>
-      <c r="D1250" s="3"/>
+      <c r="C1250" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1250" s="3">
+        <v>0</v>
+      </c>
       <c r="E1250" s="3"/>
     </row>
     <row r="1251" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18915,8 +19359,12 @@
       <c r="B1251" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1251" s="3"/>
-      <c r="D1251" s="3"/>
+      <c r="C1251" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1251" s="3">
+        <v>0</v>
+      </c>
       <c r="E1251" s="3"/>
     </row>
     <row r="1252" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18926,8 +19374,12 @@
       <c r="B1252" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1252" s="3"/>
-      <c r="D1252" s="3"/>
+      <c r="C1252" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1252" s="3">
+        <v>0</v>
+      </c>
       <c r="E1252" s="3"/>
     </row>
     <row r="1253" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18940,7 +19392,9 @@
       <c r="C1253" s="3">
         <v>1</v>
       </c>
-      <c r="D1253" s="3"/>
+      <c r="D1253" s="3">
+        <v>0</v>
+      </c>
       <c r="E1253" s="3"/>
     </row>
     <row r="1254" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18983,7 +19437,9 @@
       <c r="C1256" s="3">
         <v>1</v>
       </c>
-      <c r="D1256" s="3"/>
+      <c r="D1256" s="3">
+        <v>0</v>
+      </c>
       <c r="E1256" s="3"/>
     </row>
     <row r="1257" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18993,8 +19449,12 @@
       <c r="B1257" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1257" s="3"/>
-      <c r="D1257" s="3"/>
+      <c r="C1257" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1257" s="3">
+        <v>0</v>
+      </c>
       <c r="E1257" s="3"/>
     </row>
     <row r="1258" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19004,8 +19464,12 @@
       <c r="B1258" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1258" s="3"/>
-      <c r="D1258" s="3"/>
+      <c r="C1258" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1258" s="3">
+        <v>0</v>
+      </c>
       <c r="E1258" s="3"/>
     </row>
     <row r="1259" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19015,8 +19479,12 @@
       <c r="B1259" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1259" s="3"/>
-      <c r="D1259" s="3"/>
+      <c r="C1259" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1259" s="3">
+        <v>0</v>
+      </c>
       <c r="E1259" s="3"/>
     </row>
     <row r="1260" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19029,7 +19497,9 @@
       <c r="C1260" s="3">
         <v>1</v>
       </c>
-      <c r="D1260" s="3"/>
+      <c r="D1260" s="3">
+        <v>0</v>
+      </c>
       <c r="E1260" s="3"/>
     </row>
     <row r="1261" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19039,8 +19509,12 @@
       <c r="B1261" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1261" s="3"/>
-      <c r="D1261" s="3"/>
+      <c r="C1261" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1261" s="3">
+        <v>0</v>
+      </c>
       <c r="E1261" s="3"/>
     </row>
     <row r="1262" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19068,7 +19542,9 @@
       <c r="C1263" s="3">
         <v>1</v>
       </c>
-      <c r="D1263" s="3"/>
+      <c r="D1263" s="3">
+        <v>0</v>
+      </c>
       <c r="E1263" s="3"/>
     </row>
     <row r="1264" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19078,8 +19554,12 @@
       <c r="B1264" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1264" s="3"/>
-      <c r="D1264" s="3"/>
+      <c r="C1264" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1264" s="3">
+        <v>0</v>
+      </c>
       <c r="E1264" s="3"/>
     </row>
     <row r="1265" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19089,8 +19569,12 @@
       <c r="B1265" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1265" s="3"/>
-      <c r="D1265" s="3"/>
+      <c r="C1265" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1265" s="3">
+        <v>0</v>
+      </c>
       <c r="E1265" s="3"/>
     </row>
     <row r="1266" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19100,8 +19584,12 @@
       <c r="B1266" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1266" s="3"/>
-      <c r="D1266" s="3"/>
+      <c r="C1266" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1266" s="3">
+        <v>0</v>
+      </c>
       <c r="E1266" s="3"/>
     </row>
     <row r="1267" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19114,7 +19602,9 @@
       <c r="C1267" s="3">
         <v>1</v>
       </c>
-      <c r="D1267" s="3"/>
+      <c r="D1267" s="3">
+        <v>0</v>
+      </c>
       <c r="E1267" s="3"/>
     </row>
     <row r="1268" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19124,8 +19614,12 @@
       <c r="B1268" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1268" s="3"/>
-      <c r="D1268" s="3"/>
+      <c r="C1268" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1268" s="3">
+        <v>0</v>
+      </c>
       <c r="E1268" s="3"/>
     </row>
     <row r="1269" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19153,7 +19647,9 @@
       <c r="C1270" s="3">
         <v>1</v>
       </c>
-      <c r="D1270" s="3"/>
+      <c r="D1270" s="3">
+        <v>0</v>
+      </c>
       <c r="E1270" s="3"/>
     </row>
     <row r="1271" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19163,8 +19659,12 @@
       <c r="B1271" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1271" s="3"/>
-      <c r="D1271" s="3"/>
+      <c r="C1271" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1271" s="3">
+        <v>0</v>
+      </c>
       <c r="E1271" s="3"/>
     </row>
     <row r="1272" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19174,7 +19674,9 @@
       <c r="B1272" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1272" s="3"/>
+      <c r="C1272" s="3">
+        <v>0</v>
+      </c>
       <c r="D1272" s="3">
         <v>1</v>
       </c>
@@ -19205,7 +19707,9 @@
       <c r="C1274" s="3">
         <v>1</v>
       </c>
-      <c r="D1274" s="3"/>
+      <c r="D1274" s="3">
+        <v>0</v>
+      </c>
       <c r="E1274" s="3"/>
     </row>
     <row r="1275" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19248,7 +19752,9 @@
       <c r="C1277" s="3">
         <v>1</v>
       </c>
-      <c r="D1277" s="3"/>
+      <c r="D1277" s="3">
+        <v>0</v>
+      </c>
       <c r="E1277" s="3"/>
     </row>
     <row r="1278" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19258,8 +19764,12 @@
       <c r="B1278" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1278" s="3"/>
-      <c r="D1278" s="3"/>
+      <c r="C1278" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1278" s="3">
+        <v>0</v>
+      </c>
       <c r="E1278" s="3"/>
     </row>
     <row r="1279" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19269,8 +19779,12 @@
       <c r="B1279" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1279" s="3"/>
-      <c r="D1279" s="3"/>
+      <c r="C1279" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1279" s="3">
+        <v>0</v>
+      </c>
       <c r="E1279" s="3"/>
     </row>
     <row r="1280" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19280,8 +19794,12 @@
       <c r="B1280" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1280" s="3"/>
-      <c r="D1280" s="3"/>
+      <c r="C1280" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1280" s="3">
+        <v>0</v>
+      </c>
       <c r="E1280" s="3"/>
     </row>
     <row r="1281" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19294,7 +19812,9 @@
       <c r="C1281" s="3">
         <v>1</v>
       </c>
-      <c r="D1281" s="3"/>
+      <c r="D1281" s="3">
+        <v>0</v>
+      </c>
       <c r="E1281" s="3"/>
     </row>
     <row r="1282" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19304,8 +19824,12 @@
       <c r="B1282" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1282" s="3"/>
-      <c r="D1282" s="3"/>
+      <c r="C1282" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1282" s="3">
+        <v>0</v>
+      </c>
       <c r="E1282" s="3"/>
     </row>
     <row r="1283" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19333,7 +19857,9 @@
       <c r="C1284" s="3">
         <v>1</v>
       </c>
-      <c r="D1284" s="3"/>
+      <c r="D1284" s="3">
+        <v>0</v>
+      </c>
       <c r="E1284" s="3"/>
     </row>
     <row r="1285" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19346,7 +19872,9 @@
       <c r="C1285" s="3">
         <v>1</v>
       </c>
-      <c r="D1285" s="3"/>
+      <c r="D1285" s="3">
+        <v>0</v>
+      </c>
       <c r="E1285" s="3"/>
     </row>
     <row r="1286" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19356,7 +19884,9 @@
       <c r="B1286" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1286" s="3"/>
+      <c r="C1286" s="3">
+        <v>0</v>
+      </c>
       <c r="D1286" s="3">
         <v>1</v>
       </c>
@@ -19372,7 +19902,9 @@
       <c r="C1287" s="3">
         <v>1</v>
       </c>
-      <c r="D1287" s="3"/>
+      <c r="D1287" s="3">
+        <v>0</v>
+      </c>
       <c r="E1287" s="3"/>
     </row>
     <row r="1288" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19382,8 +19914,12 @@
       <c r="B1288" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1288" s="3"/>
-      <c r="D1288" s="3"/>
+      <c r="C1288" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1288" s="3">
+        <v>0</v>
+      </c>
       <c r="E1288" s="3"/>
     </row>
     <row r="1289" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19393,7 +19929,9 @@
       <c r="B1289" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1289" s="3"/>
+      <c r="C1289" s="3">
+        <v>0</v>
+      </c>
       <c r="D1289" s="3">
         <v>1</v>
       </c>
@@ -19424,7 +19962,9 @@
       <c r="C1291" s="3">
         <v>1</v>
       </c>
-      <c r="D1291" s="3"/>
+      <c r="D1291" s="3">
+        <v>0</v>
+      </c>
       <c r="E1291" s="3"/>
     </row>
     <row r="1292" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19434,8 +19974,12 @@
       <c r="B1292" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1292" s="3"/>
-      <c r="D1292" s="3"/>
+      <c r="C1292" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1292" s="3">
+        <v>0</v>
+      </c>
       <c r="E1292" s="3"/>
     </row>
     <row r="1293" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19448,7 +19992,9 @@
       <c r="C1293" s="3">
         <v>1</v>
       </c>
-      <c r="D1293" s="3"/>
+      <c r="D1293" s="3">
+        <v>0</v>
+      </c>
       <c r="E1293" s="3"/>
     </row>
     <row r="1294" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19458,8 +20004,12 @@
       <c r="B1294" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1294" s="3"/>
-      <c r="D1294" s="3"/>
+      <c r="C1294" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1294" s="3">
+        <v>0</v>
+      </c>
       <c r="E1294" s="3"/>
     </row>
     <row r="1295" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19469,8 +20019,12 @@
       <c r="B1295" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1295" s="3"/>
-      <c r="D1295" s="3"/>
+      <c r="C1295" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1295" s="3">
+        <v>0</v>
+      </c>
       <c r="E1295" s="3"/>
     </row>
     <row r="1296" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19480,7 +20034,9 @@
       <c r="B1296" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1296" s="3"/>
+      <c r="C1296" s="3">
+        <v>0</v>
+      </c>
       <c r="D1296" s="3">
         <v>1</v>
       </c>
@@ -19496,7 +20052,9 @@
       <c r="C1297" s="3">
         <v>1</v>
       </c>
-      <c r="D1297" s="3"/>
+      <c r="D1297" s="3">
+        <v>0</v>
+      </c>
       <c r="E1297" s="3"/>
     </row>
     <row r="1298" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19506,8 +20064,12 @@
       <c r="B1298" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1298" s="3"/>
-      <c r="D1298" s="3"/>
+      <c r="C1298" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1298" s="3">
+        <v>0</v>
+      </c>
       <c r="E1298" s="3"/>
     </row>
     <row r="1299" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19520,7 +20082,9 @@
       <c r="C1299" s="3">
         <v>1</v>
       </c>
-      <c r="D1299" s="3"/>
+      <c r="D1299" s="3">
+        <v>0</v>
+      </c>
       <c r="E1299" s="3"/>
     </row>
     <row r="1300" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19530,8 +20094,12 @@
       <c r="B1300" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1300" s="3"/>
-      <c r="D1300" s="3"/>
+      <c r="C1300" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1300" s="3">
+        <v>0</v>
+      </c>
       <c r="E1300" s="3"/>
     </row>
     <row r="1301" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19541,8 +20109,12 @@
       <c r="B1301" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1301" s="3"/>
-      <c r="D1301" s="3"/>
+      <c r="C1301" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1301" s="3">
+        <v>0</v>
+      </c>
       <c r="E1301" s="3"/>
     </row>
     <row r="1302" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19555,7 +20127,9 @@
       <c r="C1302" s="3">
         <v>1</v>
       </c>
-      <c r="D1302" s="3"/>
+      <c r="D1302" s="3">
+        <v>0</v>
+      </c>
       <c r="E1302" s="3"/>
     </row>
     <row r="1303" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19568,7 +20142,9 @@
       <c r="C1303" s="3">
         <v>1</v>
       </c>
-      <c r="D1303" s="3"/>
+      <c r="D1303" s="3">
+        <v>0</v>
+      </c>
       <c r="E1303" s="3"/>
     </row>
     <row r="1304" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19578,7 +20154,9 @@
       <c r="B1304" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1304" s="3"/>
+      <c r="C1304" s="3">
+        <v>0</v>
+      </c>
       <c r="D1304" s="3">
         <v>1</v>
       </c>
@@ -19606,8 +20184,12 @@
       <c r="B1306" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1306" s="3"/>
-      <c r="D1306" s="3"/>
+      <c r="C1306" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1306" s="3">
+        <v>0</v>
+      </c>
       <c r="E1306" s="3"/>
     </row>
     <row r="1307" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19620,7 +20202,9 @@
       <c r="C1307" s="3">
         <v>1</v>
       </c>
-      <c r="D1307" s="3"/>
+      <c r="D1307" s="3">
+        <v>0</v>
+      </c>
       <c r="E1307" s="3"/>
     </row>
     <row r="1308" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19630,8 +20214,12 @@
       <c r="B1308" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1308" s="3"/>
-      <c r="D1308" s="3"/>
+      <c r="C1308" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1308" s="3">
+        <v>0</v>
+      </c>
       <c r="E1308" s="3"/>
     </row>
     <row r="1309" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19644,7 +20232,9 @@
       <c r="C1309" s="3">
         <v>1</v>
       </c>
-      <c r="D1309" s="3"/>
+      <c r="D1309" s="3">
+        <v>0</v>
+      </c>
       <c r="E1309" s="3"/>
     </row>
     <row r="1310" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19654,7 +20244,9 @@
       <c r="B1310" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1310" s="3"/>
+      <c r="C1310" s="3">
+        <v>0</v>
+      </c>
       <c r="D1310" s="3">
         <v>1</v>
       </c>
@@ -19685,7 +20277,9 @@
       <c r="C1312" s="3">
         <v>1</v>
       </c>
-      <c r="D1312" s="3"/>
+      <c r="D1312" s="3">
+        <v>0</v>
+      </c>
       <c r="E1312" s="3"/>
     </row>
     <row r="1313" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19695,8 +20289,12 @@
       <c r="B1313" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1313" s="3"/>
-      <c r="D1313" s="3"/>
+      <c r="C1313" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1313" s="3">
+        <v>0</v>
+      </c>
       <c r="E1313" s="3"/>
     </row>
     <row r="1314" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19706,8 +20304,12 @@
       <c r="B1314" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1314" s="3"/>
-      <c r="D1314" s="3"/>
+      <c r="C1314" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1314" s="3">
+        <v>0</v>
+      </c>
       <c r="E1314" s="3"/>
     </row>
     <row r="1315" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19717,8 +20319,12 @@
       <c r="B1315" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1315" s="3"/>
-      <c r="D1315" s="3"/>
+      <c r="C1315" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1315" s="3">
+        <v>0</v>
+      </c>
       <c r="E1315" s="3"/>
     </row>
     <row r="1316" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19731,7 +20337,9 @@
       <c r="C1316" s="3">
         <v>1</v>
       </c>
-      <c r="D1316" s="3"/>
+      <c r="D1316" s="3">
+        <v>0</v>
+      </c>
       <c r="E1316" s="3"/>
     </row>
     <row r="1317" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19741,7 +20349,9 @@
       <c r="B1317" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1317" s="3"/>
+      <c r="C1317" s="3">
+        <v>0</v>
+      </c>
       <c r="D1317" s="3">
         <v>1</v>
       </c>
@@ -19769,8 +20379,12 @@
       <c r="B1319" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1319" s="3"/>
-      <c r="D1319" s="3"/>
+      <c r="C1319" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1319" s="3">
+        <v>0</v>
+      </c>
       <c r="E1319" s="3"/>
     </row>
     <row r="1320" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19783,7 +20397,9 @@
       <c r="C1320" s="3">
         <v>1</v>
       </c>
-      <c r="D1320" s="3"/>
+      <c r="D1320" s="3">
+        <v>0</v>
+      </c>
       <c r="E1320" s="3"/>
     </row>
     <row r="1321" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19793,8 +20409,12 @@
       <c r="B1321" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1321" s="3"/>
-      <c r="D1321" s="3"/>
+      <c r="C1321" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1321" s="3">
+        <v>0</v>
+      </c>
       <c r="E1321" s="3"/>
     </row>
     <row r="1322" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19804,8 +20424,12 @@
       <c r="B1322" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1322" s="3"/>
-      <c r="D1322" s="3"/>
+      <c r="C1322" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1322" s="3">
+        <v>0</v>
+      </c>
       <c r="E1322" s="3"/>
     </row>
     <row r="1323" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19815,8 +20439,12 @@
       <c r="B1323" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1323" s="3"/>
-      <c r="D1323" s="3"/>
+      <c r="C1323" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1323" s="3">
+        <v>0</v>
+      </c>
       <c r="E1323" s="3"/>
     </row>
     <row r="1324" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19826,7 +20454,9 @@
       <c r="B1324" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1324" s="3"/>
+      <c r="C1324" s="3">
+        <v>0</v>
+      </c>
       <c r="D1324" s="3">
         <v>1</v>
       </c>
@@ -19857,7 +20487,9 @@
       <c r="C1326" s="3">
         <v>1</v>
       </c>
-      <c r="D1326" s="3"/>
+      <c r="D1326" s="3">
+        <v>0</v>
+      </c>
       <c r="E1326" s="3"/>
     </row>
     <row r="1327" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19867,8 +20499,12 @@
       <c r="B1327" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1327" s="3"/>
-      <c r="D1327" s="3"/>
+      <c r="C1327" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1327" s="3">
+        <v>0</v>
+      </c>
       <c r="E1327" s="3"/>
     </row>
     <row r="1328" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19878,8 +20514,12 @@
       <c r="B1328" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1328" s="3"/>
-      <c r="D1328" s="3"/>
+      <c r="C1328" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1328" s="3">
+        <v>0</v>
+      </c>
       <c r="E1328" s="3"/>
     </row>
     <row r="1329" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19889,8 +20529,12 @@
       <c r="B1329" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1329" s="3"/>
-      <c r="D1329" s="3"/>
+      <c r="C1329" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1329" s="3">
+        <v>0</v>
+      </c>
       <c r="E1329" s="3"/>
     </row>
     <row r="1330" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19903,7 +20547,9 @@
       <c r="C1330" s="3">
         <v>1</v>
       </c>
-      <c r="D1330" s="3"/>
+      <c r="D1330" s="3">
+        <v>0</v>
+      </c>
       <c r="E1330" s="3"/>
     </row>
     <row r="1331" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19916,7 +20562,9 @@
       <c r="C1331" s="3">
         <v>1</v>
       </c>
-      <c r="D1331" s="3"/>
+      <c r="D1331" s="3">
+        <v>0</v>
+      </c>
       <c r="E1331" s="3"/>
     </row>
     <row r="1332" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19944,7 +20592,9 @@
       <c r="C1333" s="3">
         <v>1</v>
       </c>
-      <c r="D1333" s="3"/>
+      <c r="D1333" s="3">
+        <v>0</v>
+      </c>
       <c r="E1333" s="3"/>
     </row>
     <row r="1334" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19954,8 +20604,12 @@
       <c r="B1334" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1334" s="3"/>
-      <c r="D1334" s="3"/>
+      <c r="C1334" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1334" s="3">
+        <v>0</v>
+      </c>
       <c r="E1334" s="3"/>
     </row>
     <row r="1335" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19968,7 +20622,9 @@
       <c r="C1335" s="3">
         <v>1</v>
       </c>
-      <c r="D1335" s="3"/>
+      <c r="D1335" s="3">
+        <v>0</v>
+      </c>
       <c r="E1335" s="3"/>
     </row>
     <row r="1336" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19978,8 +20634,12 @@
       <c r="B1336" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1336" s="3"/>
-      <c r="D1336" s="3"/>
+      <c r="C1336" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1336" s="3">
+        <v>0</v>
+      </c>
       <c r="E1336" s="3"/>
     </row>
     <row r="1337" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -19989,8 +20649,12 @@
       <c r="B1337" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1337" s="3"/>
-      <c r="D1337" s="3"/>
+      <c r="C1337" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1337" s="3">
+        <v>0</v>
+      </c>
       <c r="E1337" s="3"/>
     </row>
     <row r="1338" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20000,8 +20664,12 @@
       <c r="B1338" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1338" s="3"/>
-      <c r="D1338" s="3"/>
+      <c r="C1338" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1338" s="3">
+        <v>0</v>
+      </c>
       <c r="E1338" s="3"/>
     </row>
     <row r="1339" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20011,7 +20679,9 @@
       <c r="B1339" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1339" s="3"/>
+      <c r="C1339" s="3">
+        <v>0</v>
+      </c>
       <c r="D1339" s="3">
         <v>1</v>
       </c>
@@ -20027,7 +20697,9 @@
       <c r="C1340" s="3">
         <v>1</v>
       </c>
-      <c r="D1340" s="3"/>
+      <c r="D1340" s="3">
+        <v>0</v>
+      </c>
       <c r="E1340" s="3"/>
     </row>
     <row r="1341" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20040,7 +20712,9 @@
       <c r="C1341" s="3">
         <v>1</v>
       </c>
-      <c r="D1341" s="3"/>
+      <c r="D1341" s="3">
+        <v>0</v>
+      </c>
       <c r="E1341" s="3"/>
     </row>
     <row r="1342" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20050,8 +20724,12 @@
       <c r="B1342" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1342" s="3"/>
-      <c r="D1342" s="3"/>
+      <c r="C1342" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1342" s="3">
+        <v>0</v>
+      </c>
       <c r="E1342" s="3"/>
     </row>
     <row r="1343" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20064,7 +20742,9 @@
       <c r="C1343" s="3">
         <v>1</v>
       </c>
-      <c r="D1343" s="3"/>
+      <c r="D1343" s="3">
+        <v>0</v>
+      </c>
       <c r="E1343" s="3"/>
     </row>
     <row r="1344" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20074,8 +20754,12 @@
       <c r="B1344" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1344" s="3"/>
-      <c r="D1344" s="3"/>
+      <c r="C1344" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1344" s="3">
+        <v>0</v>
+      </c>
       <c r="E1344" s="3"/>
     </row>
     <row r="1345" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20103,7 +20787,9 @@
       <c r="C1346" s="3">
         <v>1</v>
       </c>
-      <c r="D1346" s="3"/>
+      <c r="D1346" s="3">
+        <v>0</v>
+      </c>
       <c r="E1346" s="3"/>
     </row>
     <row r="1347" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20113,8 +20799,12 @@
       <c r="B1347" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1347" s="3"/>
-      <c r="D1347" s="3"/>
+      <c r="C1347" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1347" s="3">
+        <v>0</v>
+      </c>
       <c r="E1347" s="3"/>
     </row>
     <row r="1348" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20124,8 +20814,12 @@
       <c r="B1348" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1348" s="3"/>
-      <c r="D1348" s="3"/>
+      <c r="C1348" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1348" s="3">
+        <v>0</v>
+      </c>
       <c r="E1348" s="3"/>
     </row>
     <row r="1349" spans="1:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -20135,21 +20829,25 @@
       <c r="B1349" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1349" s="3"/>
-      <c r="D1349" s="3"/>
+      <c r="C1349" s="8">
+        <v>0</v>
+      </c>
+      <c r="D1349" s="8">
+        <v>0</v>
+      </c>
       <c r="E1349" s="3"/>
     </row>
     <row r="1350" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1350" s="4">
         <v>45917</v>
       </c>
-      <c r="B1350" s="2" t="s">
+      <c r="B1350" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1350" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1350" s="1">
+      <c r="C1350" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1350" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20157,13 +20855,13 @@
       <c r="A1351" s="4">
         <v>45918</v>
       </c>
-      <c r="B1351" s="2" t="s">
+      <c r="B1351" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1351" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1351" s="1">
+      <c r="C1351" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1351" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20171,13 +20869,13 @@
       <c r="A1352" s="4">
         <v>45919</v>
       </c>
-      <c r="B1352" s="2" t="s">
+      <c r="B1352" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1352" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1352" s="1">
+      <c r="C1352" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1352" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20185,13 +20883,13 @@
       <c r="A1353" s="4">
         <v>45920</v>
       </c>
-      <c r="B1353" s="2" t="s">
+      <c r="B1353" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1353" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1353" s="1">
+      <c r="C1353" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1353" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20199,13 +20897,13 @@
       <c r="A1354" s="4">
         <v>45921</v>
       </c>
-      <c r="B1354" s="2" t="s">
+      <c r="B1354" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1354" s="7">
-        <v>1</v>
-      </c>
-      <c r="D1354" s="1">
+      <c r="C1354" s="10">
+        <v>1</v>
+      </c>
+      <c r="D1354" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20213,13 +20911,13 @@
       <c r="A1355" s="4">
         <v>45922</v>
       </c>
-      <c r="B1355" s="2" t="s">
+      <c r="B1355" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1355" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1355" s="1">
+      <c r="C1355" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1355" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20227,13 +20925,13 @@
       <c r="A1356" s="4">
         <v>45923</v>
       </c>
-      <c r="B1356" s="2" t="s">
+      <c r="B1356" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1356" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1356" s="1">
+      <c r="C1356" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1356" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20241,13 +20939,13 @@
       <c r="A1357" s="4">
         <v>45924</v>
       </c>
-      <c r="B1357" s="2" t="s">
+      <c r="B1357" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1357" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1357" s="1">
+      <c r="C1357" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1357" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20255,13 +20953,13 @@
       <c r="A1358" s="4">
         <v>45925</v>
       </c>
-      <c r="B1358" s="2" t="s">
+      <c r="B1358" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1358" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1358" s="1">
+      <c r="C1358" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1358" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20269,13 +20967,13 @@
       <c r="A1359" s="4">
         <v>45926</v>
       </c>
-      <c r="B1359" s="2" t="s">
+      <c r="B1359" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1359" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1359" s="1">
+      <c r="C1359" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1359" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20283,13 +20981,13 @@
       <c r="A1360" s="4">
         <v>45927</v>
       </c>
-      <c r="B1360" s="2" t="s">
+      <c r="B1360" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1360" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1360" s="1">
+      <c r="C1360" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1360" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20297,13 +20995,13 @@
       <c r="A1361" s="4">
         <v>45928</v>
       </c>
-      <c r="B1361" s="2" t="s">
+      <c r="B1361" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1361" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1361" s="1">
+      <c r="C1361" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1361" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20311,13 +21009,13 @@
       <c r="A1362" s="4">
         <v>45929</v>
       </c>
-      <c r="B1362" s="2" t="s">
+      <c r="B1362" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1362" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1362" s="1">
+      <c r="C1362" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1362" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20325,13 +21023,13 @@
       <c r="A1363" s="4">
         <v>45930</v>
       </c>
-      <c r="B1363" s="2" t="s">
+      <c r="B1363" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1363" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1363" s="1">
+      <c r="C1363" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1363" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20339,13 +21037,13 @@
       <c r="A1364" s="4">
         <v>45931</v>
       </c>
-      <c r="B1364" s="2" t="s">
+      <c r="B1364" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1364" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1364" s="1">
+      <c r="C1364" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1364" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20353,13 +21051,13 @@
       <c r="A1365" s="4">
         <v>45932</v>
       </c>
-      <c r="B1365" s="2" t="s">
+      <c r="B1365" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1365" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1365" s="1">
+      <c r="C1365" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1365" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20367,13 +21065,13 @@
       <c r="A1366" s="4">
         <v>45933</v>
       </c>
-      <c r="B1366" s="2" t="s">
+      <c r="B1366" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1366" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1366" s="1">
+      <c r="C1366" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1366" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20381,13 +21079,13 @@
       <c r="A1367" s="4">
         <v>45934</v>
       </c>
-      <c r="B1367" s="2" t="s">
+      <c r="B1367" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1367" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1367" s="1">
+      <c r="C1367" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1367" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20395,13 +21093,13 @@
       <c r="A1368" s="4">
         <v>45935</v>
       </c>
-      <c r="B1368" s="2" t="s">
+      <c r="B1368" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1368" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1368" s="1">
+      <c r="C1368" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1368" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20409,13 +21107,13 @@
       <c r="A1369" s="4">
         <v>45936</v>
       </c>
-      <c r="B1369" s="2" t="s">
+      <c r="B1369" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1369" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1369" s="1">
+      <c r="C1369" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1369" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20423,13 +21121,13 @@
       <c r="A1370" s="4">
         <v>45937</v>
       </c>
-      <c r="B1370" s="2" t="s">
+      <c r="B1370" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1370" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1370" s="1">
+      <c r="C1370" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1370" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20437,13 +21135,13 @@
       <c r="A1371" s="4">
         <v>45938</v>
       </c>
-      <c r="B1371" s="2" t="s">
+      <c r="B1371" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1371" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1371" s="1">
+      <c r="C1371" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1371" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20451,13 +21149,13 @@
       <c r="A1372" s="4">
         <v>45939</v>
       </c>
-      <c r="B1372" s="2" t="s">
+      <c r="B1372" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1372" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1372" s="1">
+      <c r="C1372" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1372" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20465,13 +21163,13 @@
       <c r="A1373" s="4">
         <v>45940</v>
       </c>
-      <c r="B1373" s="2" t="s">
+      <c r="B1373" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1373" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1373" s="1">
+      <c r="C1373" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1373" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20479,13 +21177,13 @@
       <c r="A1374" s="4">
         <v>45941</v>
       </c>
-      <c r="B1374" s="2" t="s">
+      <c r="B1374" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1374" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1374" s="1">
+      <c r="C1374" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1374" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20493,13 +21191,13 @@
       <c r="A1375" s="4">
         <v>45942</v>
       </c>
-      <c r="B1375" s="2" t="s">
+      <c r="B1375" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1375" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1375" s="1">
+      <c r="C1375" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1375" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20507,13 +21205,13 @@
       <c r="A1376" s="4">
         <v>45943</v>
       </c>
-      <c r="B1376" s="2" t="s">
+      <c r="B1376" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1376" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1376" s="1">
+      <c r="C1376" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1376" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20521,13 +21219,13 @@
       <c r="A1377" s="4">
         <v>45944</v>
       </c>
-      <c r="B1377" s="2" t="s">
+      <c r="B1377" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1377" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1377" s="1">
+      <c r="C1377" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1377" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20535,13 +21233,13 @@
       <c r="A1378" s="4">
         <v>45945</v>
       </c>
-      <c r="B1378" s="2" t="s">
+      <c r="B1378" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1378" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1378" s="1">
+      <c r="C1378" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1378" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20549,13 +21247,13 @@
       <c r="A1379" s="4">
         <v>45946</v>
       </c>
-      <c r="B1379" s="2" t="s">
+      <c r="B1379" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1379" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1379" s="1">
+      <c r="C1379" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1379" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20563,13 +21261,13 @@
       <c r="A1380" s="4">
         <v>45947</v>
       </c>
-      <c r="B1380" s="2" t="s">
+      <c r="B1380" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1380" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1380" s="1">
+      <c r="C1380" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1380" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20577,13 +21275,13 @@
       <c r="A1381" s="4">
         <v>45948</v>
       </c>
-      <c r="B1381" s="2" t="s">
+      <c r="B1381" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1381" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1381" s="1">
+      <c r="C1381" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1381" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20591,13 +21289,13 @@
       <c r="A1382" s="4">
         <v>45949</v>
       </c>
-      <c r="B1382" s="2" t="s">
+      <c r="B1382" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1382" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1382" s="1">
+      <c r="C1382" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1382" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20605,13 +21303,13 @@
       <c r="A1383" s="4">
         <v>45950</v>
       </c>
-      <c r="B1383" s="2" t="s">
+      <c r="B1383" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1383" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1383" s="1">
+      <c r="C1383" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1383" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20619,13 +21317,13 @@
       <c r="A1384" s="4">
         <v>45951</v>
       </c>
-      <c r="B1384" s="2" t="s">
+      <c r="B1384" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1384" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1384" s="1">
+      <c r="C1384" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1384" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20633,13 +21331,13 @@
       <c r="A1385" s="4">
         <v>45952</v>
       </c>
-      <c r="B1385" s="2" t="s">
+      <c r="B1385" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1385" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1385" s="1">
+      <c r="C1385" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1385" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20647,13 +21345,13 @@
       <c r="A1386" s="4">
         <v>45953</v>
       </c>
-      <c r="B1386" s="2" t="s">
+      <c r="B1386" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1386" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1386" s="1">
+      <c r="C1386" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1386" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20661,13 +21359,13 @@
       <c r="A1387" s="4">
         <v>45954</v>
       </c>
-      <c r="B1387" s="2" t="s">
+      <c r="B1387" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1387" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1387" s="1">
+      <c r="C1387" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1387" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20675,13 +21373,13 @@
       <c r="A1388" s="4">
         <v>45955</v>
       </c>
-      <c r="B1388" s="2" t="s">
+      <c r="B1388" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1388" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1388" s="1">
+      <c r="C1388" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1388" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20689,13 +21387,13 @@
       <c r="A1389" s="4">
         <v>45956</v>
       </c>
-      <c r="B1389" s="2" t="s">
+      <c r="B1389" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1389" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1389" s="1">
+      <c r="C1389" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1389" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20703,13 +21401,13 @@
       <c r="A1390" s="4">
         <v>45957</v>
       </c>
-      <c r="B1390" s="2" t="s">
+      <c r="B1390" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1390" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1390" s="1">
+      <c r="C1390" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1390" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20717,13 +21415,13 @@
       <c r="A1391" s="4">
         <v>45958</v>
       </c>
-      <c r="B1391" s="2" t="s">
+      <c r="B1391" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1391" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1391" s="1">
+      <c r="C1391" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1391" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20731,13 +21429,13 @@
       <c r="A1392" s="4">
         <v>45959</v>
       </c>
-      <c r="B1392" s="2" t="s">
+      <c r="B1392" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1392" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1392" s="1">
+      <c r="C1392" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1392" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20745,13 +21443,13 @@
       <c r="A1393" s="4">
         <v>45960</v>
       </c>
-      <c r="B1393" s="2" t="s">
+      <c r="B1393" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1393" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1393" s="1">
+      <c r="C1393" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1393" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20759,13 +21457,13 @@
       <c r="A1394" s="4">
         <v>45961</v>
       </c>
-      <c r="B1394" s="2" t="s">
+      <c r="B1394" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1394" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1394" s="1">
+      <c r="C1394" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1394" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20773,13 +21471,13 @@
       <c r="A1395" s="4">
         <v>45962</v>
       </c>
-      <c r="B1395" s="2" t="s">
+      <c r="B1395" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1395" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1395" s="1">
+      <c r="C1395" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1395" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20787,13 +21485,13 @@
       <c r="A1396" s="4">
         <v>45963</v>
       </c>
-      <c r="B1396" s="2" t="s">
+      <c r="B1396" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1396" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1396" s="1">
+      <c r="C1396" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1396" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20801,13 +21499,13 @@
       <c r="A1397" s="4">
         <v>45964</v>
       </c>
-      <c r="B1397" s="2" t="s">
+      <c r="B1397" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1397" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1397" s="1">
+      <c r="C1397" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1397" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20815,13 +21513,13 @@
       <c r="A1398" s="4">
         <v>45965</v>
       </c>
-      <c r="B1398" s="2" t="s">
+      <c r="B1398" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1398" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1398" s="1">
+      <c r="C1398" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1398" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20829,13 +21527,13 @@
       <c r="A1399" s="4">
         <v>45966</v>
       </c>
-      <c r="B1399" s="2" t="s">
+      <c r="B1399" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1399" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1399" s="1">
+      <c r="C1399" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1399" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20843,13 +21541,13 @@
       <c r="A1400" s="4">
         <v>45967</v>
       </c>
-      <c r="B1400" s="2" t="s">
+      <c r="B1400" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1400" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1400" s="1">
+      <c r="C1400" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1400" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20857,13 +21555,13 @@
       <c r="A1401" s="4">
         <v>45968</v>
       </c>
-      <c r="B1401" s="2" t="s">
+      <c r="B1401" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1401" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1401" s="1">
+      <c r="C1401" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1401" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20871,13 +21569,13 @@
       <c r="A1402" s="4">
         <v>45969</v>
       </c>
-      <c r="B1402" s="2" t="s">
+      <c r="B1402" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1402" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1402" s="1">
+      <c r="C1402" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1402" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20885,13 +21583,13 @@
       <c r="A1403" s="4">
         <v>45970</v>
       </c>
-      <c r="B1403" s="2" t="s">
+      <c r="B1403" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1403" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1403" s="1">
+      <c r="C1403" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1403" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20899,13 +21597,13 @@
       <c r="A1404" s="4">
         <v>45971</v>
       </c>
-      <c r="B1404" s="2" t="s">
+      <c r="B1404" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1404" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1404" s="1">
+      <c r="C1404" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1404" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20913,13 +21611,13 @@
       <c r="A1405" s="4">
         <v>45972</v>
       </c>
-      <c r="B1405" s="2" t="s">
+      <c r="B1405" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1405" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1405" s="1">
+      <c r="C1405" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1405" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20927,13 +21625,13 @@
       <c r="A1406" s="4">
         <v>45973</v>
       </c>
-      <c r="B1406" s="2" t="s">
+      <c r="B1406" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1406" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1406" s="1">
+      <c r="C1406" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1406" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20941,13 +21639,13 @@
       <c r="A1407" s="4">
         <v>45974</v>
       </c>
-      <c r="B1407" s="2" t="s">
+      <c r="B1407" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1407" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1407" s="1">
+      <c r="C1407" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1407" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20955,13 +21653,13 @@
       <c r="A1408" s="4">
         <v>45975</v>
       </c>
-      <c r="B1408" s="2" t="s">
+      <c r="B1408" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1408" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1408" s="1">
+      <c r="C1408" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1408" s="9">
         <v>1</v>
       </c>
     </row>
@@ -20969,13 +21667,13 @@
       <c r="A1409" s="4">
         <v>45976</v>
       </c>
-      <c r="B1409" s="2" t="s">
+      <c r="B1409" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1409" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1409" s="1">
+      <c r="C1409" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1409" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20983,13 +21681,13 @@
       <c r="A1410" s="4">
         <v>45977</v>
       </c>
-      <c r="B1410" s="2" t="s">
+      <c r="B1410" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1410" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1410" s="1">
+      <c r="C1410" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1410" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20997,13 +21695,13 @@
       <c r="A1411" s="4">
         <v>45978</v>
       </c>
-      <c r="B1411" s="2" t="s">
+      <c r="B1411" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1411" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1411" s="1">
+      <c r="C1411" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1411" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21011,13 +21709,13 @@
       <c r="A1412" s="4">
         <v>45979</v>
       </c>
-      <c r="B1412" s="2" t="s">
+      <c r="B1412" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1412" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1412" s="1">
+      <c r="C1412" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1412" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21025,13 +21723,13 @@
       <c r="A1413" s="4">
         <v>45980</v>
       </c>
-      <c r="B1413" s="2" t="s">
+      <c r="B1413" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1413" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1413" s="1">
+      <c r="C1413" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1413" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21039,13 +21737,13 @@
       <c r="A1414" s="4">
         <v>45981</v>
       </c>
-      <c r="B1414" s="2" t="s">
+      <c r="B1414" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1414" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1414" s="1">
+      <c r="C1414" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1414" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21053,13 +21751,13 @@
       <c r="A1415" s="4">
         <v>45982</v>
       </c>
-      <c r="B1415" s="2" t="s">
+      <c r="B1415" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1415" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1415" s="1">
+      <c r="C1415" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1415" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21067,13 +21765,13 @@
       <c r="A1416" s="4">
         <v>45983</v>
       </c>
-      <c r="B1416" s="2" t="s">
+      <c r="B1416" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1416" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1416" s="1">
+      <c r="C1416" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1416" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21081,13 +21779,13 @@
       <c r="A1417" s="4">
         <v>45984</v>
       </c>
-      <c r="B1417" s="2" t="s">
+      <c r="B1417" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1417" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1417" s="1">
+      <c r="C1417" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1417" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21095,13 +21793,13 @@
       <c r="A1418" s="4">
         <v>45985</v>
       </c>
-      <c r="B1418" s="2" t="s">
+      <c r="B1418" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1418" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1418" s="1">
+      <c r="C1418" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1418" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21109,13 +21807,13 @@
       <c r="A1419" s="4">
         <v>45986</v>
       </c>
-      <c r="B1419" s="2" t="s">
+      <c r="B1419" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1419" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1419" s="1">
+      <c r="C1419" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1419" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21123,13 +21821,13 @@
       <c r="A1420" s="4">
         <v>45987</v>
       </c>
-      <c r="B1420" s="2" t="s">
+      <c r="B1420" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1420" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1420" s="1">
+      <c r="C1420" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1420" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21137,13 +21835,13 @@
       <c r="A1421" s="4">
         <v>45988</v>
       </c>
-      <c r="B1421" s="2" t="s">
+      <c r="B1421" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1421" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1421" s="1">
+      <c r="C1421" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1421" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21151,13 +21849,13 @@
       <c r="A1422" s="4">
         <v>45989</v>
       </c>
-      <c r="B1422" s="2" t="s">
+      <c r="B1422" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1422" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1422" s="1">
+      <c r="C1422" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1422" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21165,13 +21863,13 @@
       <c r="A1423" s="4">
         <v>45990</v>
       </c>
-      <c r="B1423" s="2" t="s">
+      <c r="B1423" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1423" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1423" s="1">
+      <c r="C1423" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1423" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21179,13 +21877,13 @@
       <c r="A1424" s="4">
         <v>45991</v>
       </c>
-      <c r="B1424" s="2" t="s">
+      <c r="B1424" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1424" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1424" s="1">
+      <c r="C1424" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1424" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21193,13 +21891,13 @@
       <c r="A1425" s="4">
         <v>45992</v>
       </c>
-      <c r="B1425" s="2" t="s">
+      <c r="B1425" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1425" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1425" s="1">
+      <c r="C1425" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1425" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21207,13 +21905,13 @@
       <c r="A1426" s="4">
         <v>45993</v>
       </c>
-      <c r="B1426" s="2" t="s">
+      <c r="B1426" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1426" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1426" s="1">
+      <c r="C1426" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1426" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21221,13 +21919,13 @@
       <c r="A1427" s="4">
         <v>45994</v>
       </c>
-      <c r="B1427" s="2" t="s">
+      <c r="B1427" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1427" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1427" s="1">
+      <c r="C1427" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1427" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21235,13 +21933,13 @@
       <c r="A1428" s="4">
         <v>45995</v>
       </c>
-      <c r="B1428" s="2" t="s">
+      <c r="B1428" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1428" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1428" s="1">
+      <c r="C1428" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1428" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21249,13 +21947,13 @@
       <c r="A1429" s="4">
         <v>45996</v>
       </c>
-      <c r="B1429" s="2" t="s">
+      <c r="B1429" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1429" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1429" s="1">
+      <c r="C1429" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1429" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21263,13 +21961,13 @@
       <c r="A1430" s="4">
         <v>45997</v>
       </c>
-      <c r="B1430" s="2" t="s">
+      <c r="B1430" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1430" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1430" s="1">
+      <c r="C1430" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1430" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21277,13 +21975,13 @@
       <c r="A1431" s="4">
         <v>45998</v>
       </c>
-      <c r="B1431" s="2" t="s">
+      <c r="B1431" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1431" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1431" s="1">
+      <c r="C1431" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1431" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21291,13 +21989,13 @@
       <c r="A1432" s="4">
         <v>45999</v>
       </c>
-      <c r="B1432" s="2" t="s">
+      <c r="B1432" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1432" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1432" s="1">
+      <c r="C1432" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1432" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21305,13 +22003,13 @@
       <c r="A1433" s="4">
         <v>46000</v>
       </c>
-      <c r="B1433" s="2" t="s">
+      <c r="B1433" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1433" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1433" s="1">
+      <c r="C1433" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1433" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21319,13 +22017,13 @@
       <c r="A1434" s="4">
         <v>46001</v>
       </c>
-      <c r="B1434" s="2" t="s">
+      <c r="B1434" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1434" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1434" s="1">
+      <c r="C1434" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1434" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21333,13 +22031,13 @@
       <c r="A1435" s="4">
         <v>46002</v>
       </c>
-      <c r="B1435" s="2" t="s">
+      <c r="B1435" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1435" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1435" s="1">
+      <c r="C1435" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1435" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21347,13 +22045,13 @@
       <c r="A1436" s="4">
         <v>46003</v>
       </c>
-      <c r="B1436" s="2" t="s">
+      <c r="B1436" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1436" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1436" s="1">
+      <c r="C1436" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1436" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21361,13 +22059,13 @@
       <c r="A1437" s="4">
         <v>46004</v>
       </c>
-      <c r="B1437" s="2" t="s">
+      <c r="B1437" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1437" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1437" s="1">
+      <c r="C1437" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1437" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21375,13 +22073,13 @@
       <c r="A1438" s="4">
         <v>46005</v>
       </c>
-      <c r="B1438" s="2" t="s">
+      <c r="B1438" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1438" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1438" s="1">
+      <c r="C1438" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1438" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21389,13 +22087,13 @@
       <c r="A1439" s="4">
         <v>46006</v>
       </c>
-      <c r="B1439" s="2" t="s">
+      <c r="B1439" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1439" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1439" s="1">
+      <c r="C1439" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1439" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21403,13 +22101,13 @@
       <c r="A1440" s="4">
         <v>46007</v>
       </c>
-      <c r="B1440" s="2" t="s">
+      <c r="B1440" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1440" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1440" s="1">
+      <c r="C1440" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1440" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21417,13 +22115,13 @@
       <c r="A1441" s="4">
         <v>46008</v>
       </c>
-      <c r="B1441" s="2" t="s">
+      <c r="B1441" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1441" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1441" s="1">
+      <c r="C1441" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1441" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21431,13 +22129,13 @@
       <c r="A1442" s="4">
         <v>46009</v>
       </c>
-      <c r="B1442" s="2" t="s">
+      <c r="B1442" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1442" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1442" s="1">
+      <c r="C1442" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1442" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21445,13 +22143,13 @@
       <c r="A1443" s="4">
         <v>46010</v>
       </c>
-      <c r="B1443" s="2" t="s">
+      <c r="B1443" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1443" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1443" s="1">
+      <c r="C1443" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1443" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21459,13 +22157,13 @@
       <c r="A1444" s="4">
         <v>46011</v>
       </c>
-      <c r="B1444" s="2" t="s">
+      <c r="B1444" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1444" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1444" s="1">
+      <c r="C1444" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1444" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21473,13 +22171,13 @@
       <c r="A1445" s="4">
         <v>46012</v>
       </c>
-      <c r="B1445" s="2" t="s">
+      <c r="B1445" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1445" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1445" s="1">
+      <c r="C1445" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1445" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21487,13 +22185,13 @@
       <c r="A1446" s="4">
         <v>46013</v>
       </c>
-      <c r="B1446" s="2" t="s">
+      <c r="B1446" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1446" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1446" s="1">
+      <c r="C1446" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1446" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21501,13 +22199,13 @@
       <c r="A1447" s="4">
         <v>46014</v>
       </c>
-      <c r="B1447" s="2" t="s">
+      <c r="B1447" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1447" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1447" s="1">
+      <c r="C1447" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1447" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21515,13 +22213,13 @@
       <c r="A1448" s="4">
         <v>46015</v>
       </c>
-      <c r="B1448" s="2" t="s">
+      <c r="B1448" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1448" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1448" s="1">
+      <c r="C1448" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1448" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21529,13 +22227,13 @@
       <c r="A1449" s="4">
         <v>46016</v>
       </c>
-      <c r="B1449" s="2" t="s">
+      <c r="B1449" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C1449" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1449" s="1">
+      <c r="C1449" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1449" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21543,13 +22241,13 @@
       <c r="A1450" s="4">
         <v>46017</v>
       </c>
-      <c r="B1450" s="2" t="s">
+      <c r="B1450" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1450" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1450" s="1">
+      <c r="C1450" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1450" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21557,13 +22255,13 @@
       <c r="A1451" s="4">
         <v>46018</v>
       </c>
-      <c r="B1451" s="2" t="s">
+      <c r="B1451" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1451" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1451" s="1">
+      <c r="C1451" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1451" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21571,13 +22269,13 @@
       <c r="A1452" s="4">
         <v>46019</v>
       </c>
-      <c r="B1452" s="2" t="s">
+      <c r="B1452" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1452" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1452" s="1">
+      <c r="C1452" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1452" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21585,13 +22283,13 @@
       <c r="A1453" s="4">
         <v>46020</v>
       </c>
-      <c r="B1453" s="2" t="s">
+      <c r="B1453" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C1453" s="1">
-        <v>1</v>
-      </c>
-      <c r="D1453" s="1">
+      <c r="C1453" s="9">
+        <v>1</v>
+      </c>
+      <c r="D1453" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21599,13 +22297,13 @@
       <c r="A1454" s="4">
         <v>46021</v>
       </c>
-      <c r="B1454" s="2" t="s">
+      <c r="B1454" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1454" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1454" s="1">
+      <c r="C1454" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1454" s="9">
         <v>0</v>
       </c>
     </row>
@@ -21613,13 +22311,13 @@
       <c r="A1455" s="4">
         <v>46022</v>
       </c>
-      <c r="B1455" s="2" t="s">
+      <c r="B1455" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1455" s="1">
-        <v>0</v>
-      </c>
-      <c r="D1455" s="1">
+      <c r="C1455" s="9">
+        <v>0</v>
+      </c>
+      <c r="D1455" s="9">
         <v>1</v>
       </c>
     </row>
